--- a/Research/Instructions/Ricoh 5A22 Instructions Native SNES.xlsx
+++ b/Research/Instructions/Ricoh 5A22 Instructions Native SNES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Projects\BirdSNES\Research\Instructions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEF22C7E-9550-439B-97A1-54546A29E133}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{205BA3BB-EB62-4B6B-A5DA-6917C074B35F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{7ED93F2B-FF78-48E4-8428-9E2E36877943}"/>
   </bookViews>
@@ -21453,9 +21453,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -21463,6 +21460,9 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -22095,10 +22095,10 @@
     </row>
     <row r="61" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="17"/>
-      <c r="B61" s="33" t="s">
+      <c r="B61" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="C61" s="34"/>
+      <c r="C61" s="33"/>
     </row>
     <row r="62" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
@@ -22253,14 +22253,14 @@
         <v>8.1</v>
       </c>
       <c r="B78" s="7"/>
-      <c r="C78" s="32" t="s">
+      <c r="C78" s="35" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="79" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="3"/>
       <c r="B79" s="7"/>
-      <c r="C79" s="32"/>
+      <c r="C79" s="35"/>
     </row>
     <row r="80" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="3">
@@ -22637,14 +22637,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B190" s="7"/>
-      <c r="C190" s="32" t="s">
+      <c r="C190" s="35" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="191" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="3"/>
       <c r="B191" s="7"/>
-      <c r="C191" s="32"/>
+      <c r="C191" s="35"/>
     </row>
     <row r="192" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="3">
@@ -22783,14 +22783,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B249" s="7"/>
-      <c r="C249" s="32" t="s">
+      <c r="C249" s="35" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="250" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="3"/>
       <c r="B250" s="7"/>
-      <c r="C250" s="32"/>
+      <c r="C250" s="35"/>
     </row>
     <row r="251" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="3">
@@ -22981,14 +22981,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B308" s="7"/>
-      <c r="C308" s="32" t="s">
+      <c r="C308" s="35" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="309" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="3"/>
       <c r="B309" s="7"/>
-      <c r="C309" s="32"/>
+      <c r="C309" s="35"/>
     </row>
     <row r="310" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="3">
@@ -23127,19 +23127,19 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B367" s="7"/>
-      <c r="C367" s="32" t="s">
+      <c r="C367" s="35" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="368" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A368" s="3"/>
       <c r="B368" s="7"/>
-      <c r="C368" s="32"/>
+      <c r="C368" s="35"/>
     </row>
     <row r="369" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A369" s="3"/>
       <c r="B369" s="7"/>
-      <c r="C369" s="32"/>
+      <c r="C369" s="35"/>
     </row>
     <row r="370" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A370" s="3">
@@ -23372,7 +23372,7 @@
       <c r="A431" s="25">
         <v>7.2</v>
       </c>
-      <c r="B431" s="35" t="s">
+      <c r="B431" s="34" t="s">
         <v>342</v>
       </c>
       <c r="C431" s="8" t="s">
@@ -23381,7 +23381,7 @@
     </row>
     <row r="432" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A432" s="25"/>
-      <c r="B432" s="35"/>
+      <c r="B432" s="34"/>
       <c r="C432" s="8"/>
     </row>
     <row r="433" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23389,14 +23389,14 @@
         <v>8.1</v>
       </c>
       <c r="B433" s="7"/>
-      <c r="C433" s="32" t="s">
+      <c r="C433" s="35" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="434" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A434" s="3"/>
       <c r="B434" s="7"/>
-      <c r="C434" s="32"/>
+      <c r="C434" s="35"/>
     </row>
     <row r="435" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A435" s="3">
@@ -23604,14 +23604,14 @@
         <v>3.1</v>
       </c>
       <c r="B540" s="7"/>
-      <c r="C540" s="32" t="s">
+      <c r="C540" s="35" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="541" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A541" s="3"/>
       <c r="B541" s="7"/>
-      <c r="C541" s="32"/>
+      <c r="C541" s="35"/>
     </row>
     <row r="542" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A542" s="3">
@@ -23696,14 +23696,14 @@
         <v>2.1</v>
       </c>
       <c r="B597" s="7"/>
-      <c r="C597" s="32" t="s">
+      <c r="C597" s="35" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="598" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A598" s="3"/>
       <c r="B598" s="7"/>
-      <c r="C598" s="32"/>
+      <c r="C598" s="35"/>
     </row>
     <row r="599" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A599" s="3">
@@ -23917,7 +23917,7 @@
         <v>90</v>
       </c>
       <c r="C716" s="2" t="s">
-        <v>25</v>
+        <v>276</v>
       </c>
     </row>
     <row r="717" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23951,7 +23951,7 @@
       <c r="A720" s="23">
         <v>4.2</v>
       </c>
-      <c r="B720" s="35" t="s">
+      <c r="B720" s="34" t="s">
         <v>514</v>
       </c>
       <c r="C720" s="8" t="s">
@@ -23960,7 +23960,7 @@
     </row>
     <row r="721" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A721" s="23"/>
-      <c r="B721" s="35"/>
+      <c r="B721" s="34"/>
       <c r="C721" s="8"/>
     </row>
     <row r="722" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23992,7 +23992,7 @@
       <c r="A725" s="25">
         <v>6.2</v>
       </c>
-      <c r="B725" s="35" t="s">
+      <c r="B725" s="34" t="s">
         <v>515</v>
       </c>
       <c r="C725" s="8" t="s">
@@ -24001,7 +24001,7 @@
     </row>
     <row r="726" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A726" s="25"/>
-      <c r="B726" s="35"/>
+      <c r="B726" s="34"/>
       <c r="C726" s="8"/>
     </row>
     <row r="727" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -24124,7 +24124,7 @@
         <v>90</v>
       </c>
       <c r="C775" s="2" t="s">
-        <v>25</v>
+        <v>276</v>
       </c>
     </row>
     <row r="776" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -24158,7 +24158,7 @@
       <c r="A779" s="25">
         <v>4.2</v>
       </c>
-      <c r="B779" s="35" t="s">
+      <c r="B779" s="34" t="s">
         <v>514</v>
       </c>
       <c r="C779" s="8" t="s">
@@ -24167,7 +24167,7 @@
     </row>
     <row r="780" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A780" s="25"/>
-      <c r="B780" s="35"/>
+      <c r="B780" s="34"/>
       <c r="C780" s="8"/>
     </row>
     <row r="781" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -24175,14 +24175,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B781" s="7"/>
-      <c r="C781" s="32" t="s">
+      <c r="C781" s="35" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="782" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A782" s="3"/>
       <c r="B782" s="7"/>
-      <c r="C782" s="32"/>
+      <c r="C782" s="35"/>
     </row>
     <row r="783" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A783" s="3">
@@ -24279,7 +24279,7 @@
         <v>90</v>
       </c>
       <c r="C834" s="2" t="s">
-        <v>25</v>
+        <v>276</v>
       </c>
     </row>
     <row r="835" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -24313,7 +24313,7 @@
       <c r="A838" s="23">
         <v>4.2</v>
       </c>
-      <c r="B838" s="35" t="s">
+      <c r="B838" s="34" t="s">
         <v>514</v>
       </c>
       <c r="C838" s="8" t="s">
@@ -24322,7 +24322,7 @@
     </row>
     <row r="839" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A839" s="23"/>
-      <c r="B839" s="35"/>
+      <c r="B839" s="34"/>
       <c r="C839" s="8"/>
     </row>
     <row r="840" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -24330,19 +24330,19 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B840" s="7"/>
-      <c r="C840" s="32" t="s">
+      <c r="C840" s="35" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="841" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A841" s="3"/>
       <c r="B841" s="7"/>
-      <c r="C841" s="32"/>
+      <c r="C841" s="35"/>
     </row>
     <row r="842" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A842" s="3"/>
       <c r="B842" s="7"/>
-      <c r="C842" s="32"/>
+      <c r="C842" s="35"/>
     </row>
     <row r="843" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A843" s="3">
@@ -24364,7 +24364,7 @@
       <c r="A845" s="25">
         <v>6.2</v>
       </c>
-      <c r="B845" s="35" t="s">
+      <c r="B845" s="34" t="s">
         <v>515</v>
       </c>
       <c r="C845" s="8" t="s">
@@ -24373,7 +24373,7 @@
     </row>
     <row r="846" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A846" s="25"/>
-      <c r="B846" s="35"/>
+      <c r="B846" s="34"/>
       <c r="C846" s="8"/>
     </row>
     <row r="847" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -24496,7 +24496,7 @@
         <v>90</v>
       </c>
       <c r="C893" s="2" t="s">
-        <v>25</v>
+        <v>276</v>
       </c>
     </row>
     <row r="894" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -24550,7 +24550,7 @@
       <c r="A899" s="25">
         <v>5.2</v>
       </c>
-      <c r="B899" s="35" t="s">
+      <c r="B899" s="34" t="s">
         <v>343</v>
       </c>
       <c r="C899" s="8" t="s">
@@ -24559,7 +24559,7 @@
     </row>
     <row r="900" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A900" s="25"/>
-      <c r="B900" s="35"/>
+      <c r="B900" s="34"/>
       <c r="C900" s="8"/>
     </row>
     <row r="901" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -24567,14 +24567,14 @@
         <v>6.1</v>
       </c>
       <c r="B901" s="7"/>
-      <c r="C901" s="32" t="s">
+      <c r="C901" s="35" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="902" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A902" s="3"/>
       <c r="B902" s="7"/>
-      <c r="C902" s="32"/>
+      <c r="C902" s="35"/>
     </row>
     <row r="903" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A903" s="3">
@@ -24712,10 +24712,10 @@
     </row>
     <row r="1005" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1005" s="17"/>
-      <c r="B1005" s="33" t="s">
+      <c r="B1005" s="32" t="s">
         <v>122</v>
       </c>
-      <c r="C1005" s="34"/>
+      <c r="C1005" s="33"/>
     </row>
     <row r="1006" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1006" s="5" t="s">
@@ -24886,7 +24886,7 @@
       <c r="A1025" s="25">
         <v>7.2</v>
       </c>
-      <c r="B1025" s="35" t="s">
+      <c r="B1025" s="34" t="s">
         <v>342</v>
       </c>
       <c r="C1025" s="8" t="s">
@@ -24895,7 +24895,7 @@
     </row>
     <row r="1026" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1026" s="25"/>
-      <c r="B1026" s="35"/>
+      <c r="B1026" s="34"/>
       <c r="C1026" s="8"/>
     </row>
     <row r="1027" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -24903,14 +24903,14 @@
         <v>8.1</v>
       </c>
       <c r="B1027" s="7"/>
-      <c r="C1027" s="32" t="s">
+      <c r="C1027" s="35" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="1028" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1028" s="3"/>
       <c r="B1028" s="7"/>
-      <c r="C1028" s="32"/>
+      <c r="C1028" s="35"/>
     </row>
     <row r="1029" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1029" s="3">
@@ -25085,14 +25085,14 @@
         <v>7.1</v>
       </c>
       <c r="B1079" s="7"/>
-      <c r="C1079" s="32" t="s">
+      <c r="C1079" s="35" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="1080" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1080" s="3"/>
       <c r="B1080" s="7"/>
-      <c r="C1080" s="32"/>
+      <c r="C1080" s="35"/>
     </row>
     <row r="1081" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1081" s="3">
@@ -25125,10 +25125,10 @@
     </row>
     <row r="1123" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1123" s="17"/>
-      <c r="B1123" s="33" t="s">
+      <c r="B1123" s="32" t="s">
         <v>127</v>
       </c>
-      <c r="C1123" s="34"/>
+      <c r="C1123" s="33"/>
     </row>
     <row r="1124" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1124" s="5" t="s">
@@ -25290,7 +25290,7 @@
       <c r="A1142" s="25">
         <v>7.2</v>
       </c>
-      <c r="B1142" s="35" t="s">
+      <c r="B1142" s="34" t="s">
         <v>342</v>
       </c>
       <c r="C1142" s="11" t="s">
@@ -25299,7 +25299,7 @@
     </row>
     <row r="1143" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1143" s="25"/>
-      <c r="B1143" s="35"/>
+      <c r="B1143" s="34"/>
       <c r="C1143" s="11"/>
     </row>
     <row r="1144" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -25307,14 +25307,14 @@
         <v>8.1</v>
       </c>
       <c r="B1144" s="7"/>
-      <c r="C1144" s="32" t="s">
+      <c r="C1144" s="35" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="1145" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1145" s="3"/>
       <c r="B1145" s="7"/>
-      <c r="C1145" s="32"/>
+      <c r="C1145" s="35"/>
     </row>
     <row r="1146" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1146" s="3">
@@ -25347,10 +25347,10 @@
     </row>
     <row r="1182" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1182" s="17"/>
-      <c r="B1182" s="33" t="s">
+      <c r="B1182" s="32" t="s">
         <v>80</v>
       </c>
-      <c r="C1182" s="34"/>
+      <c r="C1182" s="33"/>
     </row>
     <row r="1183" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1183" s="5" t="s">
@@ -25453,14 +25453,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B1193" s="7"/>
-      <c r="C1193" s="32" t="s">
+      <c r="C1193" s="35" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="1194" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1194" s="3"/>
       <c r="B1194" s="7"/>
-      <c r="C1194" s="32"/>
+      <c r="C1194" s="35"/>
     </row>
     <row r="1195" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1195" s="3">
@@ -25665,14 +25665,14 @@
         <v>6.1</v>
       </c>
       <c r="B1254" s="7"/>
-      <c r="C1254" s="32" t="s">
+      <c r="C1254" s="35" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="1255" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1255" s="3"/>
       <c r="B1255" s="7"/>
-      <c r="C1255" s="32"/>
+      <c r="C1255" s="35"/>
     </row>
     <row r="1256" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1256" s="3">
@@ -25705,10 +25705,10 @@
     </row>
     <row r="1300" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1300" s="17"/>
-      <c r="B1300" s="33" t="s">
+      <c r="B1300" s="32" t="s">
         <v>223</v>
       </c>
-      <c r="C1300" s="34"/>
+      <c r="C1300" s="33"/>
     </row>
     <row r="1301" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1301" s="5" t="s">
@@ -25825,19 +25825,19 @@
         <v>6.1</v>
       </c>
       <c r="B1313" s="7"/>
-      <c r="C1313" s="32" t="s">
+      <c r="C1313" s="35" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="1314" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1314" s="3"/>
       <c r="B1314" s="7"/>
-      <c r="C1314" s="32"/>
+      <c r="C1314" s="35"/>
     </row>
     <row r="1315" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1315" s="3"/>
       <c r="B1315" s="7"/>
-      <c r="C1315" s="32"/>
+      <c r="C1315" s="35"/>
     </row>
     <row r="1316" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1316" s="3">
@@ -25922,10 +25922,10 @@
     </row>
     <row r="1359" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1359" s="17"/>
-      <c r="B1359" s="33" t="s">
+      <c r="B1359" s="32" t="s">
         <v>139</v>
       </c>
-      <c r="C1359" s="34"/>
+      <c r="C1359" s="33"/>
     </row>
     <row r="1360" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1360" s="5" t="s">
@@ -26086,7 +26086,7 @@
       <c r="A1377" s="25">
         <v>7.2</v>
       </c>
-      <c r="B1377" s="35" t="s">
+      <c r="B1377" s="34" t="s">
         <v>342</v>
       </c>
       <c r="C1377" s="8" t="s">
@@ -26095,7 +26095,7 @@
     </row>
     <row r="1378" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1378" s="25"/>
-      <c r="B1378" s="35"/>
+      <c r="B1378" s="34"/>
       <c r="C1378" s="8"/>
     </row>
     <row r="1379" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -26103,14 +26103,14 @@
         <v>8.1</v>
       </c>
       <c r="B1379" s="7"/>
-      <c r="C1379" s="32" t="s">
+      <c r="C1379" s="35" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="1380" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1380" s="3"/>
       <c r="B1380" s="7"/>
-      <c r="C1380" s="32"/>
+      <c r="C1380" s="35"/>
     </row>
     <row r="1381" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1381" s="3">
@@ -26230,10 +26230,10 @@
     </row>
     <row r="1477" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1477" s="17"/>
-      <c r="B1477" s="33" t="s">
+      <c r="B1477" s="32" t="s">
         <v>142</v>
       </c>
-      <c r="C1477" s="34"/>
+      <c r="C1477" s="33"/>
     </row>
     <row r="1478" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1478" s="5" t="s">
@@ -26370,7 +26370,7 @@
       <c r="A1493" s="25">
         <v>5.2</v>
       </c>
-      <c r="B1493" s="35" t="s">
+      <c r="B1493" s="34" t="s">
         <v>342</v>
       </c>
       <c r="C1493" s="11" t="s">
@@ -26379,7 +26379,7 @@
     </row>
     <row r="1494" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1494" s="25"/>
-      <c r="B1494" s="35"/>
+      <c r="B1494" s="34"/>
       <c r="C1494" s="11"/>
     </row>
     <row r="1495" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -26387,14 +26387,14 @@
         <v>6.1</v>
       </c>
       <c r="B1495" s="7"/>
-      <c r="C1495" s="32" t="s">
+      <c r="C1495" s="35" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="1496" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1496" s="3"/>
       <c r="B1496" s="7"/>
-      <c r="C1496" s="32"/>
+      <c r="C1496" s="35"/>
     </row>
     <row r="1497" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1497" s="3">
@@ -26479,14 +26479,14 @@
         <v>2.1</v>
       </c>
       <c r="B1541" s="7"/>
-      <c r="C1541" s="32" t="s">
+      <c r="C1541" s="35" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="1542" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1542" s="3"/>
       <c r="B1542" s="7"/>
-      <c r="C1542" s="32"/>
+      <c r="C1542" s="35"/>
     </row>
     <row r="1543" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1543" s="3">
@@ -26606,10 +26606,10 @@
     </row>
     <row r="1654" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1654" s="17"/>
-      <c r="B1654" s="33" t="s">
+      <c r="B1654" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="C1654" s="34"/>
+      <c r="C1654" s="33"/>
     </row>
     <row r="1655" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1655" s="5" t="s">
@@ -26670,7 +26670,7 @@
         <v>90</v>
       </c>
       <c r="C1660" s="2" t="s">
-        <v>25</v>
+        <v>276</v>
       </c>
     </row>
     <row r="1661" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -26704,7 +26704,7 @@
       <c r="A1664" s="23">
         <v>4.2</v>
       </c>
-      <c r="B1664" s="35" t="s">
+      <c r="B1664" s="34" t="s">
         <v>514</v>
       </c>
       <c r="C1664" s="11" t="s">
@@ -26713,7 +26713,7 @@
     </row>
     <row r="1665" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1665" s="23"/>
-      <c r="B1665" s="35"/>
+      <c r="B1665" s="34"/>
       <c r="C1665" s="11"/>
     </row>
     <row r="1666" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -26721,14 +26721,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B1666" s="7"/>
-      <c r="C1666" s="32" t="s">
+      <c r="C1666" s="35" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="1667" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1667" s="3"/>
       <c r="B1667" s="7"/>
-      <c r="C1667" s="32"/>
+      <c r="C1667" s="35"/>
     </row>
     <row r="1668" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1668" s="3">
@@ -26750,7 +26750,7 @@
       <c r="A1670" s="23">
         <v>6.2</v>
       </c>
-      <c r="B1670" s="35" t="s">
+      <c r="B1670" s="34" t="s">
         <v>515</v>
       </c>
       <c r="C1670" s="8" t="s">
@@ -26759,7 +26759,7 @@
     </row>
     <row r="1671" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1671" s="23"/>
-      <c r="B1671" s="35"/>
+      <c r="B1671" s="34"/>
       <c r="C1671" s="8"/>
     </row>
     <row r="1672" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -26958,7 +26958,7 @@
       <c r="A1729" s="25">
         <v>5.2</v>
       </c>
-      <c r="B1729" s="35" t="s">
+      <c r="B1729" s="34" t="s">
         <v>342</v>
       </c>
       <c r="C1729" s="11" t="s">
@@ -26967,7 +26967,7 @@
     </row>
     <row r="1730" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1730" s="25"/>
-      <c r="B1730" s="35"/>
+      <c r="B1730" s="34"/>
       <c r="C1730" s="11"/>
     </row>
     <row r="1731" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -26975,14 +26975,14 @@
         <v>6.1</v>
       </c>
       <c r="B1731" s="7"/>
-      <c r="C1731" s="32" t="s">
+      <c r="C1731" s="35" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="1732" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1732" s="3"/>
       <c r="B1732" s="7"/>
-      <c r="C1732" s="32"/>
+      <c r="C1732" s="35"/>
     </row>
     <row r="1733" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1733" s="3">
@@ -27015,10 +27015,10 @@
     </row>
     <row r="1772" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1772" s="17"/>
-      <c r="B1772" s="33" t="s">
+      <c r="B1772" s="32" t="s">
         <v>153</v>
       </c>
-      <c r="C1772" s="34"/>
+      <c r="C1772" s="33"/>
     </row>
     <row r="1773" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1773" s="5" t="s">
@@ -27148,7 +27148,7 @@
       <c r="A1787" s="23">
         <v>5.2</v>
       </c>
-      <c r="B1787" s="35" t="s">
+      <c r="B1787" s="34" t="s">
         <v>342</v>
       </c>
       <c r="C1787" s="11" t="s">
@@ -27157,7 +27157,7 @@
     </row>
     <row r="1788" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1788" s="23"/>
-      <c r="B1788" s="35"/>
+      <c r="B1788" s="34"/>
       <c r="C1788" s="11"/>
     </row>
     <row r="1789" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -27165,19 +27165,19 @@
         <v>6.1</v>
       </c>
       <c r="B1789" s="7"/>
-      <c r="C1789" s="32" t="s">
+      <c r="C1789" s="35" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="1790" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1790" s="3"/>
       <c r="B1790" s="7"/>
-      <c r="C1790" s="32"/>
+      <c r="C1790" s="35"/>
     </row>
     <row r="1791" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1791" s="3"/>
       <c r="B1791" s="7"/>
-      <c r="C1791" s="32"/>
+      <c r="C1791" s="35"/>
     </row>
     <row r="1792" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1792" s="3">
@@ -27199,7 +27199,7 @@
       <c r="A1794" s="23">
         <v>7.2</v>
       </c>
-      <c r="B1794" s="35" t="s">
+      <c r="B1794" s="34" t="s">
         <v>344</v>
       </c>
       <c r="C1794" s="11" t="s">
@@ -27208,7 +27208,7 @@
     </row>
     <row r="1795" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1795" s="23"/>
-      <c r="B1795" s="35"/>
+      <c r="B1795" s="34"/>
       <c r="C1795" s="11"/>
     </row>
     <row r="1796" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -27406,7 +27406,7 @@
       <c r="A1846" s="25">
         <v>5.2</v>
       </c>
-      <c r="B1846" s="35" t="s">
+      <c r="B1846" s="34" t="s">
         <v>342</v>
       </c>
       <c r="C1846" s="11" t="s">
@@ -27415,7 +27415,7 @@
     </row>
     <row r="1847" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1847" s="25"/>
-      <c r="B1847" s="35"/>
+      <c r="B1847" s="34"/>
       <c r="C1847" s="11"/>
     </row>
     <row r="1848" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -27423,14 +27423,14 @@
         <v>6.1</v>
       </c>
       <c r="B1848" s="7"/>
-      <c r="C1848" s="32" t="s">
+      <c r="C1848" s="35" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="1849" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1849" s="3"/>
       <c r="B1849" s="7"/>
-      <c r="C1849" s="32"/>
+      <c r="C1849" s="35"/>
     </row>
     <row r="1850" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1850" s="3">
@@ -27527,7 +27527,7 @@
         <v>90</v>
       </c>
       <c r="C1896" s="2" t="s">
-        <v>25</v>
+        <v>276</v>
       </c>
     </row>
     <row r="1897" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -27628,10 +27628,10 @@
     </row>
     <row r="1949" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1949" s="17"/>
-      <c r="B1949" s="33" t="s">
+      <c r="B1949" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="C1949" s="34"/>
+      <c r="C1949" s="33"/>
     </row>
     <row r="1950" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1950" s="5" t="s">
@@ -27786,14 +27786,14 @@
         <v>8.1</v>
       </c>
       <c r="B1966" s="7"/>
-      <c r="C1966" s="32" t="s">
+      <c r="C1966" s="35" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="1967" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1967" s="3"/>
       <c r="B1967" s="7"/>
-      <c r="C1967" s="32"/>
+      <c r="C1967" s="35"/>
     </row>
     <row r="1968" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1968" s="3">
@@ -27826,10 +27826,10 @@
     </row>
     <row r="2008" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2008" s="17"/>
-      <c r="B2008" s="33" t="s">
+      <c r="B2008" s="32" t="s">
         <v>166</v>
       </c>
-      <c r="C2008" s="34"/>
+      <c r="C2008" s="33"/>
     </row>
     <row r="2009" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2009" s="5" t="s">
@@ -27890,7 +27890,7 @@
         <v>90</v>
       </c>
       <c r="C2014" s="2" t="s">
-        <v>25</v>
+        <v>276</v>
       </c>
     </row>
     <row r="2015" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -28129,14 +28129,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B2078" s="7"/>
-      <c r="C2078" s="32" t="s">
+      <c r="C2078" s="35" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="2079" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2079" s="3"/>
       <c r="B2079" s="7"/>
-      <c r="C2079" s="32"/>
+      <c r="C2079" s="35"/>
     </row>
     <row r="2080" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2080" s="3">
@@ -28275,19 +28275,19 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B2137" s="7"/>
-      <c r="C2137" s="32" t="s">
+      <c r="C2137" s="35" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="2138" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2138" s="3"/>
       <c r="B2138" s="7"/>
-      <c r="C2138" s="32"/>
+      <c r="C2138" s="35"/>
     </row>
     <row r="2139" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2139" s="3"/>
       <c r="B2139" s="7"/>
-      <c r="C2139" s="32"/>
+      <c r="C2139" s="35"/>
     </row>
     <row r="2140" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2140" s="3">
@@ -28426,14 +28426,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B2196" s="7"/>
-      <c r="C2196" s="32" t="s">
+      <c r="C2196" s="35" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="2197" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2197" s="3"/>
       <c r="B2197" s="7"/>
-      <c r="C2197" s="32"/>
+      <c r="C2197" s="35"/>
     </row>
     <row r="2198" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2198" s="3">
@@ -28466,10 +28466,10 @@
     </row>
     <row r="2244" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2244" s="17"/>
-      <c r="B2244" s="33" t="s">
+      <c r="B2244" s="32" t="s">
         <v>80</v>
       </c>
-      <c r="C2244" s="34"/>
+      <c r="C2244" s="33"/>
     </row>
     <row r="2245" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2245" s="5" t="s">
@@ -28572,19 +28572,19 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B2255" s="7"/>
-      <c r="C2255" s="32" t="s">
+      <c r="C2255" s="35" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="2256" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2256" s="3"/>
       <c r="B2256" s="7"/>
-      <c r="C2256" s="32"/>
+      <c r="C2256" s="35"/>
     </row>
     <row r="2257" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2257" s="3"/>
       <c r="B2257" s="7"/>
-      <c r="C2257" s="32"/>
+      <c r="C2257" s="35"/>
     </row>
     <row r="2258" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2258" s="3">
@@ -28669,10 +28669,10 @@
     </row>
     <row r="2303" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2303" s="17"/>
-      <c r="B2303" s="33" t="s">
+      <c r="B2303" s="32" t="s">
         <v>87</v>
       </c>
-      <c r="C2303" s="34"/>
+      <c r="C2303" s="33"/>
     </row>
     <row r="2304" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2304" s="5" t="s">
@@ -28817,7 +28817,7 @@
       <c r="A2319" s="25">
         <v>7.2</v>
       </c>
-      <c r="B2319" s="35" t="s">
+      <c r="B2319" s="34" t="s">
         <v>342</v>
       </c>
       <c r="C2319" s="8" t="s">
@@ -28826,7 +28826,7 @@
     </row>
     <row r="2320" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2320" s="25"/>
-      <c r="B2320" s="35"/>
+      <c r="B2320" s="34"/>
       <c r="C2320" s="8"/>
     </row>
     <row r="2321" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -28834,14 +28834,14 @@
         <v>8.1</v>
       </c>
       <c r="B2321" s="7"/>
-      <c r="C2321" s="32" t="s">
+      <c r="C2321" s="35" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="2322" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2322" s="3"/>
       <c r="B2322" s="7"/>
-      <c r="C2322" s="32"/>
+      <c r="C2322" s="35"/>
     </row>
     <row r="2323" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2323" s="3">
@@ -29063,14 +29063,14 @@
         <v>3.1</v>
       </c>
       <c r="B2428" s="7"/>
-      <c r="C2428" s="32" t="s">
+      <c r="C2428" s="35" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="2429" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2429" s="3"/>
       <c r="B2429" s="7"/>
-      <c r="C2429" s="32"/>
+      <c r="C2429" s="35"/>
     </row>
     <row r="2430" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2430" s="3">
@@ -29155,19 +29155,19 @@
         <v>2.1</v>
       </c>
       <c r="B2485" s="7"/>
-      <c r="C2485" s="32" t="s">
+      <c r="C2485" s="35" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="2486" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2486" s="3"/>
       <c r="B2486" s="7"/>
-      <c r="C2486" s="32"/>
+      <c r="C2486" s="35"/>
     </row>
     <row r="2487" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2487" s="3"/>
       <c r="B2487" s="7"/>
-      <c r="C2487" s="32"/>
+      <c r="C2487" s="35"/>
     </row>
     <row r="2488" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2488" s="3">
@@ -29200,10 +29200,10 @@
     </row>
     <row r="2539" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2539" s="17"/>
-      <c r="B2539" s="33" t="s">
+      <c r="B2539" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="C2539" s="34"/>
+      <c r="C2539" s="33"/>
     </row>
     <row r="2540" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2540" s="5" t="s">
@@ -29397,7 +29397,7 @@
         <v>90</v>
       </c>
       <c r="C2604" s="2" t="s">
-        <v>25</v>
+        <v>276</v>
       </c>
     </row>
     <row r="2605" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -29431,7 +29431,7 @@
       <c r="A2608" s="25">
         <v>4.2</v>
       </c>
-      <c r="B2608" s="35" t="s">
+      <c r="B2608" s="34" t="s">
         <v>514</v>
       </c>
       <c r="C2608" s="11" t="s">
@@ -29440,7 +29440,7 @@
     </row>
     <row r="2609" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2609" s="25"/>
-      <c r="B2609" s="35"/>
+      <c r="B2609" s="34"/>
       <c r="C2609" s="11"/>
     </row>
     <row r="2610" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -29448,19 +29448,19 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B2610" s="7"/>
-      <c r="C2610" s="32" t="s">
+      <c r="C2610" s="35" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="2611" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2611" s="3"/>
       <c r="B2611" s="7"/>
-      <c r="C2611" s="32"/>
+      <c r="C2611" s="35"/>
     </row>
     <row r="2612" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2612" s="3"/>
       <c r="B2612" s="7"/>
-      <c r="C2612" s="32"/>
+      <c r="C2612" s="35"/>
     </row>
     <row r="2613" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2613" s="3">
@@ -29557,7 +29557,7 @@
         <v>90</v>
       </c>
       <c r="C2663" s="2" t="s">
-        <v>25</v>
+        <v>276</v>
       </c>
     </row>
     <row r="2664" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -29591,7 +29591,7 @@
       <c r="A2667" s="25">
         <v>4.2</v>
       </c>
-      <c r="B2667" s="35" t="s">
+      <c r="B2667" s="34" t="s">
         <v>514</v>
       </c>
       <c r="C2667" s="11" t="s">
@@ -29600,7 +29600,7 @@
     </row>
     <row r="2668" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2668" s="25"/>
-      <c r="B2668" s="35"/>
+      <c r="B2668" s="34"/>
       <c r="C2668" s="11"/>
     </row>
     <row r="2669" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -29608,14 +29608,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B2669" s="7"/>
-      <c r="C2669" s="32" t="s">
+      <c r="C2669" s="35" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="2670" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2670" s="3"/>
       <c r="B2670" s="7"/>
-      <c r="C2670" s="32"/>
+      <c r="C2670" s="35"/>
     </row>
     <row r="2671" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2671" s="3">
@@ -29648,10 +29648,10 @@
     </row>
     <row r="2716" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2716" s="17"/>
-      <c r="B2716" s="33" t="s">
+      <c r="B2716" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="C2716" s="34"/>
+      <c r="C2716" s="33"/>
     </row>
     <row r="2717" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2717" s="5" t="s">
@@ -29712,7 +29712,7 @@
         <v>90</v>
       </c>
       <c r="C2722" s="2" t="s">
-        <v>25</v>
+        <v>276</v>
       </c>
     </row>
     <row r="2723" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -29746,7 +29746,7 @@
       <c r="A2726" s="23">
         <v>4.2</v>
       </c>
-      <c r="B2726" s="35" t="s">
+      <c r="B2726" s="34" t="s">
         <v>514</v>
       </c>
       <c r="C2726" s="8" t="s">
@@ -29755,7 +29755,7 @@
     </row>
     <row r="2727" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2727" s="23"/>
-      <c r="B2727" s="35"/>
+      <c r="B2727" s="34"/>
       <c r="C2727" s="8"/>
     </row>
     <row r="2728" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -29763,19 +29763,19 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B2728" s="7"/>
-      <c r="C2728" s="32" t="s">
+      <c r="C2728" s="35" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="2729" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2729" s="3"/>
       <c r="B2729" s="7"/>
-      <c r="C2729" s="32"/>
+      <c r="C2729" s="35"/>
     </row>
     <row r="2730" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2730" s="3"/>
       <c r="B2730" s="7"/>
-      <c r="C2730" s="32"/>
+      <c r="C2730" s="35"/>
     </row>
     <row r="2731" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2731" s="3">
@@ -29797,7 +29797,7 @@
       <c r="A2733" s="23">
         <v>6.2</v>
       </c>
-      <c r="B2733" s="35" t="s">
+      <c r="B2733" s="34" t="s">
         <v>515</v>
       </c>
       <c r="C2733" s="8" t="s">
@@ -29806,7 +29806,7 @@
     </row>
     <row r="2734" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2734" s="23"/>
-      <c r="B2734" s="35"/>
+      <c r="B2734" s="34"/>
       <c r="C2734" s="8"/>
     </row>
     <row r="2735" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -29865,10 +29865,10 @@
     </row>
     <row r="2775" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2775" s="17"/>
-      <c r="B2775" s="33" t="s">
+      <c r="B2775" s="32" t="s">
         <v>108</v>
       </c>
-      <c r="C2775" s="34"/>
+      <c r="C2775" s="33"/>
     </row>
     <row r="2776" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2776" s="5" t="s">
@@ -29929,7 +29929,7 @@
         <v>90</v>
       </c>
       <c r="C2781" s="2" t="s">
-        <v>25</v>
+        <v>276</v>
       </c>
     </row>
     <row r="2782" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -29983,7 +29983,7 @@
       <c r="A2787" s="25">
         <v>5.2</v>
       </c>
-      <c r="B2787" s="35" t="s">
+      <c r="B2787" s="34" t="s">
         <v>343</v>
       </c>
       <c r="C2787" s="11" t="s">
@@ -29992,7 +29992,7 @@
     </row>
     <row r="2788" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2788" s="25"/>
-      <c r="B2788" s="35"/>
+      <c r="B2788" s="34"/>
       <c r="C2788" s="11"/>
     </row>
     <row r="2789" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -30000,14 +30000,14 @@
         <v>6.1</v>
       </c>
       <c r="B2789" s="7"/>
-      <c r="C2789" s="32" t="s">
+      <c r="C2789" s="35" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="2790" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2790" s="3"/>
       <c r="B2790" s="7"/>
-      <c r="C2790" s="32"/>
+      <c r="C2790" s="35"/>
     </row>
     <row r="2791" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2791" s="3">
@@ -30145,10 +30145,10 @@
     </row>
     <row r="2893" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2893" s="17"/>
-      <c r="B2893" s="33" t="s">
+      <c r="B2893" s="32" t="s">
         <v>122</v>
       </c>
-      <c r="C2893" s="34"/>
+      <c r="C2893" s="33"/>
     </row>
     <row r="2894" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2894" s="5" t="s">
@@ -30319,7 +30319,7 @@
       <c r="A2913" s="25">
         <v>7.2</v>
       </c>
-      <c r="B2913" s="35" t="s">
+      <c r="B2913" s="34" t="s">
         <v>342</v>
       </c>
       <c r="C2913" s="11" t="s">
@@ -30328,7 +30328,7 @@
     </row>
     <row r="2914" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2914" s="25"/>
-      <c r="B2914" s="35"/>
+      <c r="B2914" s="34"/>
       <c r="C2914" s="11"/>
     </row>
     <row r="2915" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -30336,14 +30336,14 @@
         <v>8.1</v>
       </c>
       <c r="B2915" s="7"/>
-      <c r="C2915" s="32" t="s">
+      <c r="C2915" s="35" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="2916" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2916" s="3"/>
       <c r="B2916" s="7"/>
-      <c r="C2916" s="32"/>
+      <c r="C2916" s="35"/>
     </row>
     <row r="2917" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2917" s="3">
@@ -30376,10 +30376,10 @@
     </row>
     <row r="2952" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2952" s="17"/>
-      <c r="B2952" s="33" t="s">
+      <c r="B2952" s="32" t="s">
         <v>124</v>
       </c>
-      <c r="C2952" s="34"/>
+      <c r="C2952" s="33"/>
     </row>
     <row r="2953" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2953" s="5" t="s">
@@ -30518,14 +30518,14 @@
         <v>7.1</v>
       </c>
       <c r="B2967" s="7"/>
-      <c r="C2967" s="32" t="s">
+      <c r="C2967" s="35" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="2968" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2968" s="3"/>
       <c r="B2968" s="7"/>
-      <c r="C2968" s="32"/>
+      <c r="C2968" s="35"/>
     </row>
     <row r="2969" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2969" s="3">
@@ -30558,10 +30558,10 @@
     </row>
     <row r="3011" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3011" s="17"/>
-      <c r="B3011" s="33" t="s">
+      <c r="B3011" s="32" t="s">
         <v>127</v>
       </c>
-      <c r="C3011" s="34"/>
+      <c r="C3011" s="33"/>
     </row>
     <row r="3012" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3012" s="5" t="s">
@@ -30716,7 +30716,7 @@
       <c r="A3029" s="25">
         <v>7.2</v>
       </c>
-      <c r="B3029" s="35" t="s">
+      <c r="B3029" s="34" t="s">
         <v>342</v>
       </c>
       <c r="C3029" s="11" t="s">
@@ -30725,7 +30725,7 @@
     </row>
     <row r="3030" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3030" s="25"/>
-      <c r="B3030" s="35"/>
+      <c r="B3030" s="34"/>
       <c r="C3030" s="11"/>
     </row>
     <row r="3031" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -30733,14 +30733,14 @@
         <v>8.1</v>
       </c>
       <c r="B3031" s="7"/>
-      <c r="C3031" s="32" t="s">
+      <c r="C3031" s="35" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="3032" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3032" s="3"/>
       <c r="B3032" s="7"/>
-      <c r="C3032" s="32"/>
+      <c r="C3032" s="35"/>
     </row>
     <row r="3033" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3033" s="3">
@@ -30893,19 +30893,19 @@
         <v>6.1</v>
       </c>
       <c r="B3083" s="7"/>
-      <c r="C3083" s="32" t="s">
+      <c r="C3083" s="35" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="3084" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3084" s="3"/>
       <c r="B3084" s="7"/>
-      <c r="C3084" s="32"/>
+      <c r="C3084" s="35"/>
     </row>
     <row r="3085" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3085" s="3"/>
       <c r="B3085" s="7"/>
-      <c r="C3085" s="32"/>
+      <c r="C3085" s="35"/>
     </row>
     <row r="3086" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3086" s="3">
@@ -31058,14 +31058,14 @@
         <v>6.1</v>
       </c>
       <c r="B3142" s="7"/>
-      <c r="C3142" s="32" t="s">
+      <c r="C3142" s="35" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="3143" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3143" s="3"/>
       <c r="B3143" s="7"/>
-      <c r="C3143" s="32"/>
+      <c r="C3143" s="35"/>
     </row>
     <row r="3144" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3144" s="3">
@@ -31098,10 +31098,10 @@
     </row>
     <row r="3188" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3188" s="17"/>
-      <c r="B3188" s="33" t="s">
+      <c r="B3188" s="32" t="s">
         <v>137</v>
       </c>
-      <c r="C3188" s="34"/>
+      <c r="C3188" s="33"/>
     </row>
     <row r="3189" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3189" s="5" t="s">
@@ -31218,19 +31218,19 @@
         <v>6.1</v>
       </c>
       <c r="B3201" s="7"/>
-      <c r="C3201" s="32" t="s">
+      <c r="C3201" s="35" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="3202" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3202" s="3"/>
       <c r="B3202" s="7"/>
-      <c r="C3202" s="32"/>
+      <c r="C3202" s="35"/>
     </row>
     <row r="3203" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3203" s="3"/>
       <c r="B3203" s="7"/>
-      <c r="C3203" s="32"/>
+      <c r="C3203" s="35"/>
     </row>
     <row r="3204" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3204" s="3">
@@ -31315,10 +31315,10 @@
     </row>
     <row r="3247" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3247" s="17"/>
-      <c r="B3247" s="33" t="s">
+      <c r="B3247" s="32" t="s">
         <v>139</v>
       </c>
-      <c r="C3247" s="34"/>
+      <c r="C3247" s="33"/>
     </row>
     <row r="3248" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3248" s="5" t="s">
@@ -31479,7 +31479,7 @@
       <c r="A3265" s="25">
         <v>7.2</v>
       </c>
-      <c r="B3265" s="35" t="s">
+      <c r="B3265" s="34" t="s">
         <v>342</v>
       </c>
       <c r="C3265" s="11" t="s">
@@ -31488,7 +31488,7 @@
     </row>
     <row r="3266" spans="1:3" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3266" s="25"/>
-      <c r="B3266" s="35"/>
+      <c r="B3266" s="34"/>
       <c r="C3266" s="11"/>
     </row>
     <row r="3267" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -31496,14 +31496,14 @@
         <v>8.1</v>
       </c>
       <c r="B3267" s="7"/>
-      <c r="C3267" s="32" t="s">
+      <c r="C3267" s="35" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="3268" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3268" s="3"/>
       <c r="B3268" s="7"/>
-      <c r="C3268" s="32"/>
+      <c r="C3268" s="35"/>
     </row>
     <row r="3269" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3269" s="3">
@@ -31623,10 +31623,10 @@
     </row>
     <row r="3365" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3365" s="17"/>
-      <c r="B3365" s="33" t="s">
+      <c r="B3365" s="32" t="s">
         <v>142</v>
       </c>
-      <c r="C3365" s="34"/>
+      <c r="C3365" s="33"/>
     </row>
     <row r="3366" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3366" s="5" t="s">
@@ -31763,7 +31763,7 @@
       <c r="A3381" s="25">
         <v>5.2</v>
       </c>
-      <c r="B3381" s="35" t="s">
+      <c r="B3381" s="34" t="s">
         <v>342</v>
       </c>
       <c r="C3381" s="8" t="s">
@@ -31772,7 +31772,7 @@
     </row>
     <row r="3382" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3382" s="25"/>
-      <c r="B3382" s="35"/>
+      <c r="B3382" s="34"/>
       <c r="C3382" s="8"/>
     </row>
     <row r="3383" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -31780,14 +31780,14 @@
         <v>6.1</v>
       </c>
       <c r="B3383" s="7"/>
-      <c r="C3383" s="32" t="s">
+      <c r="C3383" s="35" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="3384" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3384" s="3"/>
       <c r="B3384" s="7"/>
-      <c r="C3384" s="32"/>
+      <c r="C3384" s="35"/>
     </row>
     <row r="3385" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3385" s="3">
@@ -31872,14 +31872,14 @@
         <v>2.1</v>
       </c>
       <c r="B3429" s="7"/>
-      <c r="C3429" s="32" t="s">
+      <c r="C3429" s="35" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="3430" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3430" s="3"/>
       <c r="B3430" s="7"/>
-      <c r="C3430" s="32"/>
+      <c r="C3430" s="35"/>
     </row>
     <row r="3431" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3431" s="3">
@@ -32139,7 +32139,7 @@
       <c r="A3558" s="25">
         <v>5.2</v>
       </c>
-      <c r="B3558" s="35" t="s">
+      <c r="B3558" s="34" t="s">
         <v>342</v>
       </c>
       <c r="C3558" s="11" t="s">
@@ -32148,7 +32148,7 @@
     </row>
     <row r="3559" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3559" s="25"/>
-      <c r="B3559" s="35"/>
+      <c r="B3559" s="34"/>
       <c r="C3559" s="11"/>
     </row>
     <row r="3560" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -32156,19 +32156,19 @@
         <v>6.1</v>
       </c>
       <c r="B3560" s="7"/>
-      <c r="C3560" s="32" t="s">
+      <c r="C3560" s="35" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="3561" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3561" s="3"/>
       <c r="B3561" s="7"/>
-      <c r="C3561" s="32"/>
+      <c r="C3561" s="35"/>
     </row>
     <row r="3562" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3562" s="3"/>
       <c r="B3562" s="7"/>
-      <c r="C3562" s="32"/>
+      <c r="C3562" s="35"/>
     </row>
     <row r="3563" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3563" s="3">
@@ -32334,7 +32334,7 @@
       <c r="A3616" s="25">
         <v>5.2</v>
       </c>
-      <c r="B3616" s="35" t="s">
+      <c r="B3616" s="34" t="s">
         <v>342</v>
       </c>
       <c r="C3616" s="11" t="s">
@@ -32343,7 +32343,7 @@
     </row>
     <row r="3617" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3617" s="25"/>
-      <c r="B3617" s="35"/>
+      <c r="B3617" s="34"/>
       <c r="C3617" s="11"/>
     </row>
     <row r="3618" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -32351,14 +32351,14 @@
         <v>6.1</v>
       </c>
       <c r="B3618" s="7"/>
-      <c r="C3618" s="32" t="s">
+      <c r="C3618" s="35" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="3619" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3619" s="3"/>
       <c r="B3619" s="7"/>
-      <c r="C3619" s="32"/>
+      <c r="C3619" s="35"/>
     </row>
     <row r="3620" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3620" s="3">
@@ -32391,10 +32391,10 @@
     </row>
     <row r="3660" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3660" s="17"/>
-      <c r="B3660" s="33" t="s">
+      <c r="B3660" s="32" t="s">
         <v>153</v>
       </c>
-      <c r="C3660" s="34"/>
+      <c r="C3660" s="33"/>
     </row>
     <row r="3661" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3661" s="5" t="s">
@@ -32517,7 +32517,7 @@
       <c r="A3674" s="23">
         <v>5.2</v>
       </c>
-      <c r="B3674" s="35" t="s">
+      <c r="B3674" s="34" t="s">
         <v>342</v>
       </c>
       <c r="C3674" s="11" t="s">
@@ -32526,7 +32526,7 @@
     </row>
     <row r="3675" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3675" s="23"/>
-      <c r="B3675" s="35"/>
+      <c r="B3675" s="34"/>
       <c r="C3675" s="11"/>
     </row>
     <row r="3676" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -32534,19 +32534,19 @@
         <v>6.1</v>
       </c>
       <c r="B3676" s="7"/>
-      <c r="C3676" s="32" t="s">
+      <c r="C3676" s="35" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="3677" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3677" s="3"/>
       <c r="B3677" s="7"/>
-      <c r="C3677" s="32"/>
+      <c r="C3677" s="35"/>
     </row>
     <row r="3678" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3678" s="3"/>
       <c r="B3678" s="7"/>
-      <c r="C3678" s="32"/>
+      <c r="C3678" s="35"/>
     </row>
     <row r="3679" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3679" s="3">
@@ -32568,7 +32568,7 @@
       <c r="A3681" s="23">
         <v>7.2</v>
       </c>
-      <c r="B3681" s="35" t="s">
+      <c r="B3681" s="34" t="s">
         <v>344</v>
       </c>
       <c r="C3681" s="11" t="s">
@@ -32577,7 +32577,7 @@
     </row>
     <row r="3682" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3682" s="23"/>
-      <c r="B3682" s="35"/>
+      <c r="B3682" s="34"/>
       <c r="C3682" s="11"/>
     </row>
     <row r="3683" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -32636,10 +32636,10 @@
     </row>
     <row r="3719" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3719" s="17"/>
-      <c r="B3719" s="33" t="s">
+      <c r="B3719" s="32" t="s">
         <v>158</v>
       </c>
-      <c r="C3719" s="34"/>
+      <c r="C3719" s="33"/>
     </row>
     <row r="3720" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3720" s="5" t="s">
@@ -32768,7 +32768,7 @@
       <c r="A3733" s="25">
         <v>5.2</v>
       </c>
-      <c r="B3733" s="35" t="s">
+      <c r="B3733" s="34" t="s">
         <v>342</v>
       </c>
       <c r="C3733" s="8" t="s">
@@ -32777,7 +32777,7 @@
     </row>
     <row r="3734" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3734" s="25"/>
-      <c r="B3734" s="35"/>
+      <c r="B3734" s="34"/>
       <c r="C3734" s="8"/>
     </row>
     <row r="3735" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -32785,14 +32785,14 @@
         <v>6.1</v>
       </c>
       <c r="B3735" s="7"/>
-      <c r="C3735" s="32" t="s">
+      <c r="C3735" s="35" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="3736" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3736" s="3"/>
       <c r="B3736" s="7"/>
-      <c r="C3736" s="32"/>
+      <c r="C3736" s="35"/>
     </row>
     <row r="3737" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3737" s="3">
@@ -32998,10 +32998,10 @@
     </row>
     <row r="3837" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3837" s="17"/>
-      <c r="B3837" s="33" t="s">
+      <c r="B3837" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="C3837" s="34"/>
+      <c r="C3837" s="33"/>
     </row>
     <row r="3838" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3838" s="5" t="s">
@@ -33156,14 +33156,14 @@
         <v>8.1</v>
       </c>
       <c r="B3854" s="7"/>
-      <c r="C3854" s="32" t="s">
+      <c r="C3854" s="35" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="3855" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3855" s="3"/>
       <c r="B3855" s="7"/>
-      <c r="C3855" s="32"/>
+      <c r="C3855" s="35"/>
     </row>
     <row r="3856" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3856" s="3">
@@ -33283,10 +33283,10 @@
     </row>
     <row r="3955" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3955" s="17"/>
-      <c r="B3955" s="33" t="s">
+      <c r="B3955" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="C3955" s="34"/>
+      <c r="C3955" s="33"/>
     </row>
     <row r="3956" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3956" s="5" t="s">
@@ -33387,14 +33387,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B3966" s="7"/>
-      <c r="C3966" s="32" t="s">
+      <c r="C3966" s="35" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="3967" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3967" s="3"/>
       <c r="B3967" s="7"/>
-      <c r="C3967" s="32"/>
+      <c r="C3967" s="35"/>
     </row>
     <row r="3968" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3968" s="3">
@@ -33427,10 +33427,10 @@
     </row>
     <row r="4014" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4014" s="17"/>
-      <c r="B4014" s="33" t="s">
+      <c r="B4014" s="32" t="s">
         <v>256</v>
       </c>
-      <c r="C4014" s="34"/>
+      <c r="C4014" s="33"/>
     </row>
     <row r="4015" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4015" s="5" t="s">
@@ -33537,14 +33537,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B4025" s="7"/>
-      <c r="C4025" s="32" t="s">
+      <c r="C4025" s="35" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="4026" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4026" s="3"/>
       <c r="B4026" s="7"/>
-      <c r="C4026" s="32"/>
+      <c r="C4026" s="35"/>
     </row>
     <row r="4027" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4027" s="3">
@@ -33605,10 +33605,10 @@
     </row>
     <row r="4073" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4073" s="17"/>
-      <c r="B4073" s="33" t="s">
+      <c r="B4073" s="32" t="s">
         <v>82</v>
       </c>
-      <c r="C4073" s="34"/>
+      <c r="C4073" s="33"/>
     </row>
     <row r="4074" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4074" s="5" t="s">
@@ -33711,14 +33711,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B4084" s="7"/>
-      <c r="C4084" s="32" t="s">
+      <c r="C4084" s="35" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="4085" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4085" s="3"/>
       <c r="B4085" s="7"/>
-      <c r="C4085" s="32"/>
+      <c r="C4085" s="35"/>
     </row>
     <row r="4086" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4086" s="3">
@@ -33751,10 +33751,10 @@
     </row>
     <row r="4132" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4132" s="17"/>
-      <c r="B4132" s="33" t="s">
+      <c r="B4132" s="32" t="s">
         <v>80</v>
       </c>
-      <c r="C4132" s="34"/>
+      <c r="C4132" s="33"/>
     </row>
     <row r="4133" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4133" s="5" t="s">
@@ -33857,19 +33857,19 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B4143" s="7"/>
-      <c r="C4143" s="32" t="s">
+      <c r="C4143" s="35" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="4144" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4144" s="3"/>
       <c r="B4144" s="7"/>
-      <c r="C4144" s="32"/>
+      <c r="C4144" s="35"/>
     </row>
     <row r="4145" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4145" s="3"/>
       <c r="B4145" s="7"/>
-      <c r="C4145" s="32"/>
+      <c r="C4145" s="35"/>
     </row>
     <row r="4146" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4146" s="3">
@@ -33954,10 +33954,10 @@
     </row>
     <row r="4191" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4191" s="17"/>
-      <c r="B4191" s="33" t="s">
+      <c r="B4191" s="32" t="s">
         <v>87</v>
       </c>
-      <c r="C4191" s="34"/>
+      <c r="C4191" s="33"/>
     </row>
     <row r="4192" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4192" s="5" t="s">
@@ -34102,7 +34102,7 @@
       <c r="A4207" s="25">
         <v>7.2</v>
       </c>
-      <c r="B4207" s="35" t="s">
+      <c r="B4207" s="34" t="s">
         <v>342</v>
       </c>
       <c r="C4207" s="11" t="s">
@@ -34111,7 +34111,7 @@
     </row>
     <row r="4208" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4208" s="25"/>
-      <c r="B4208" s="35"/>
+      <c r="B4208" s="34"/>
       <c r="C4208" s="11"/>
     </row>
     <row r="4209" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -34119,14 +34119,14 @@
         <v>8.1</v>
       </c>
       <c r="B4209" s="7"/>
-      <c r="C4209" s="32" t="s">
+      <c r="C4209" s="35" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="4210" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4210" s="3"/>
       <c r="B4210" s="7"/>
-      <c r="C4210" s="32"/>
+      <c r="C4210" s="35"/>
     </row>
     <row r="4211" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4211" s="3">
@@ -34354,14 +34354,14 @@
         <v>3.1</v>
       </c>
       <c r="B4316" s="7"/>
-      <c r="C4316" s="32" t="s">
+      <c r="C4316" s="35" t="s">
         <v>368</v>
       </c>
     </row>
     <row r="4317" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4317" s="3"/>
       <c r="B4317" s="7"/>
-      <c r="C4317" s="32"/>
+      <c r="C4317" s="35"/>
     </row>
     <row r="4318" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4318" s="3">
@@ -34446,14 +34446,14 @@
         <v>2.1</v>
       </c>
       <c r="B4373" s="7"/>
-      <c r="C4373" s="32" t="s">
+      <c r="C4373" s="35" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="4374" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4374" s="3"/>
       <c r="B4374" s="7"/>
-      <c r="C4374" s="32"/>
+      <c r="C4374" s="35"/>
     </row>
     <row r="4375" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4375" s="3">
@@ -34651,7 +34651,7 @@
         <v>90</v>
       </c>
       <c r="C4492" s="2" t="s">
-        <v>25</v>
+        <v>276</v>
       </c>
     </row>
     <row r="4493" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -34758,7 +34758,7 @@
         <v>90</v>
       </c>
       <c r="C4551" s="2" t="s">
-        <v>25</v>
+        <v>276</v>
       </c>
     </row>
     <row r="4552" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -34792,7 +34792,7 @@
       <c r="A4555" s="25">
         <v>4.2</v>
       </c>
-      <c r="B4555" s="35" t="s">
+      <c r="B4555" s="34" t="s">
         <v>514</v>
       </c>
       <c r="C4555" s="11" t="s">
@@ -34801,7 +34801,7 @@
     </row>
     <row r="4556" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4556" s="25"/>
-      <c r="B4556" s="35"/>
+      <c r="B4556" s="34"/>
       <c r="C4556" s="11"/>
     </row>
     <row r="4557" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -34809,14 +34809,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B4557" s="7"/>
-      <c r="C4557" s="32" t="s">
+      <c r="C4557" s="35" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="4558" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4558" s="3"/>
       <c r="B4558" s="7"/>
-      <c r="C4558" s="32"/>
+      <c r="C4558" s="35"/>
     </row>
     <row r="4559" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4559" s="3">
@@ -34849,10 +34849,10 @@
     </row>
     <row r="4604" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4604" s="17"/>
-      <c r="B4604" s="33" t="s">
+      <c r="B4604" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="C4604" s="34"/>
+      <c r="C4604" s="33"/>
     </row>
     <row r="4605" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4605" s="5" t="s">
@@ -34913,7 +34913,7 @@
         <v>90</v>
       </c>
       <c r="C4610" s="2" t="s">
-        <v>25</v>
+        <v>276</v>
       </c>
     </row>
     <row r="4611" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -34947,7 +34947,7 @@
       <c r="A4614" s="23">
         <v>4.2</v>
       </c>
-      <c r="B4614" s="35" t="s">
+      <c r="B4614" s="34" t="s">
         <v>514</v>
       </c>
       <c r="C4614" s="11" t="s">
@@ -34956,7 +34956,7 @@
     </row>
     <row r="4615" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4615" s="23"/>
-      <c r="B4615" s="35"/>
+      <c r="B4615" s="34"/>
       <c r="C4615" s="11"/>
     </row>
     <row r="4616" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -34964,19 +34964,19 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B4616" s="7"/>
-      <c r="C4616" s="32" t="s">
+      <c r="C4616" s="35" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="4617" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4617" s="3"/>
       <c r="B4617" s="7"/>
-      <c r="C4617" s="32"/>
+      <c r="C4617" s="35"/>
     </row>
     <row r="4618" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4618" s="3"/>
       <c r="B4618" s="7"/>
-      <c r="C4618" s="32"/>
+      <c r="C4618" s="35"/>
     </row>
     <row r="4619" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4619" s="3">
@@ -34998,7 +34998,7 @@
       <c r="A4621" s="23">
         <v>6.2</v>
       </c>
-      <c r="B4621" s="35" t="s">
+      <c r="B4621" s="34" t="s">
         <v>515</v>
       </c>
       <c r="C4621" s="11" t="s">
@@ -35007,7 +35007,7 @@
     </row>
     <row r="4622" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4622" s="23"/>
-      <c r="B4622" s="35"/>
+      <c r="B4622" s="34"/>
       <c r="C4622" s="11"/>
     </row>
     <row r="4623" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -35066,10 +35066,10 @@
     </row>
     <row r="4663" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4663" s="17"/>
-      <c r="B4663" s="33" t="s">
+      <c r="B4663" s="32" t="s">
         <v>108</v>
       </c>
-      <c r="C4663" s="34"/>
+      <c r="C4663" s="33"/>
     </row>
     <row r="4664" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4664" s="5" t="s">
@@ -35130,7 +35130,7 @@
         <v>90</v>
       </c>
       <c r="C4669" s="2" t="s">
-        <v>25</v>
+        <v>276</v>
       </c>
     </row>
     <row r="4670" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -35184,7 +35184,7 @@
       <c r="A4675" s="25">
         <v>5.2</v>
       </c>
-      <c r="B4675" s="35" t="s">
+      <c r="B4675" s="34" t="s">
         <v>343</v>
       </c>
       <c r="C4675" s="11" t="s">
@@ -35193,7 +35193,7 @@
     </row>
     <row r="4676" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4676" s="25"/>
-      <c r="B4676" s="35"/>
+      <c r="B4676" s="34"/>
       <c r="C4676" s="11"/>
     </row>
     <row r="4677" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -35201,14 +35201,14 @@
         <v>6.1</v>
       </c>
       <c r="B4677" s="7"/>
-      <c r="C4677" s="32" t="s">
+      <c r="C4677" s="35" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="4678" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4678" s="3"/>
       <c r="B4678" s="7"/>
-      <c r="C4678" s="32"/>
+      <c r="C4678" s="35"/>
     </row>
     <row r="4679" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4679" s="3">
@@ -35346,10 +35346,10 @@
     </row>
     <row r="4781" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4781" s="17"/>
-      <c r="B4781" s="33" t="s">
+      <c r="B4781" s="32" t="s">
         <v>122</v>
       </c>
-      <c r="C4781" s="34"/>
+      <c r="C4781" s="33"/>
     </row>
     <row r="4782" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4782" s="5" t="s">
@@ -35520,7 +35520,7 @@
       <c r="A4801" s="25">
         <v>7.2</v>
       </c>
-      <c r="B4801" s="35" t="s">
+      <c r="B4801" s="34" t="s">
         <v>342</v>
       </c>
       <c r="C4801" s="11" t="s">
@@ -35529,7 +35529,7 @@
     </row>
     <row r="4802" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4802" s="25"/>
-      <c r="B4802" s="35"/>
+      <c r="B4802" s="34"/>
       <c r="C4802" s="11"/>
     </row>
     <row r="4803" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -35537,14 +35537,14 @@
         <v>8.1</v>
       </c>
       <c r="B4803" s="7"/>
-      <c r="C4803" s="32" t="s">
+      <c r="C4803" s="35" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="4804" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4804" s="3"/>
       <c r="B4804" s="7"/>
-      <c r="C4804" s="32"/>
+      <c r="C4804" s="35"/>
     </row>
     <row r="4805" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4805" s="3">
@@ -35719,14 +35719,14 @@
         <v>7.1</v>
       </c>
       <c r="B4855" s="7"/>
-      <c r="C4855" s="32" t="s">
+      <c r="C4855" s="35" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="4856" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4856" s="3"/>
       <c r="B4856" s="7"/>
-      <c r="C4856" s="32"/>
+      <c r="C4856" s="35"/>
     </row>
     <row r="4857" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4857" s="3">
@@ -35759,10 +35759,10 @@
     </row>
     <row r="4899" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4899" s="17"/>
-      <c r="B4899" s="33" t="s">
+      <c r="B4899" s="32" t="s">
         <v>127</v>
       </c>
-      <c r="C4899" s="34"/>
+      <c r="C4899" s="33"/>
     </row>
     <row r="4900" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4900" s="5" t="s">
@@ -35917,7 +35917,7 @@
       <c r="A4917" s="25">
         <v>7.2</v>
       </c>
-      <c r="B4917" s="35" t="s">
+      <c r="B4917" s="34" t="s">
         <v>342</v>
       </c>
       <c r="C4917" s="11" t="s">
@@ -35926,7 +35926,7 @@
     </row>
     <row r="4918" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4918" s="25"/>
-      <c r="B4918" s="35"/>
+      <c r="B4918" s="34"/>
       <c r="C4918" s="11"/>
     </row>
     <row r="4919" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -35934,14 +35934,14 @@
         <v>8.1</v>
       </c>
       <c r="B4919" s="7"/>
-      <c r="C4919" s="32" t="s">
+      <c r="C4919" s="35" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="4920" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4920" s="3"/>
       <c r="B4920" s="7"/>
-      <c r="C4920" s="32"/>
+      <c r="C4920" s="35"/>
     </row>
     <row r="4921" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4921" s="3">
@@ -35974,10 +35974,10 @@
     </row>
     <row r="4958" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4958" s="17"/>
-      <c r="B4958" s="33" t="s">
+      <c r="B4958" s="32" t="s">
         <v>261</v>
       </c>
-      <c r="C4958" s="34"/>
+      <c r="C4958" s="33"/>
     </row>
     <row r="4959" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4959" s="5" t="s">
@@ -36084,14 +36084,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B4969" s="7"/>
-      <c r="C4969" s="32" t="s">
+      <c r="C4969" s="35" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="4970" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4970" s="3"/>
       <c r="B4970" s="7"/>
-      <c r="C4970" s="32"/>
+      <c r="C4970" s="35"/>
     </row>
     <row r="4971" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4971" s="3">
@@ -36272,14 +36272,14 @@
         <v>6.1</v>
       </c>
       <c r="B5030" s="7"/>
-      <c r="C5030" s="32" t="s">
+      <c r="C5030" s="35" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="5031" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5031" s="3"/>
       <c r="B5031" s="7"/>
-      <c r="C5031" s="32"/>
+      <c r="C5031" s="35"/>
     </row>
     <row r="5032" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5032" s="3">
@@ -36312,10 +36312,10 @@
     </row>
     <row r="5076" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5076" s="17"/>
-      <c r="B5076" s="33" t="s">
+      <c r="B5076" s="32" t="s">
         <v>223</v>
       </c>
-      <c r="C5076" s="34"/>
+      <c r="C5076" s="33"/>
     </row>
     <row r="5077" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5077" s="5" t="s">
@@ -36432,19 +36432,19 @@
         <v>6.1</v>
       </c>
       <c r="B5089" s="7"/>
-      <c r="C5089" s="32" t="s">
+      <c r="C5089" s="35" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="5090" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5090" s="3"/>
       <c r="B5090" s="7"/>
-      <c r="C5090" s="32"/>
+      <c r="C5090" s="35"/>
     </row>
     <row r="5091" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5091" s="3"/>
       <c r="B5091" s="7"/>
-      <c r="C5091" s="32"/>
+      <c r="C5091" s="35"/>
     </row>
     <row r="5092" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5092" s="3">
@@ -36693,7 +36693,7 @@
       <c r="A5153" s="25">
         <v>7.2</v>
       </c>
-      <c r="B5153" s="35" t="s">
+      <c r="B5153" s="34" t="s">
         <v>342</v>
       </c>
       <c r="C5153" s="11" t="s">
@@ -36702,7 +36702,7 @@
     </row>
     <row r="5154" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5154" s="25"/>
-      <c r="B5154" s="35"/>
+      <c r="B5154" s="34"/>
       <c r="C5154" s="11"/>
     </row>
     <row r="5155" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -36710,14 +36710,14 @@
         <v>8.1</v>
       </c>
       <c r="B5155" s="7"/>
-      <c r="C5155" s="32" t="s">
+      <c r="C5155" s="35" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="5156" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5156" s="3"/>
       <c r="B5156" s="7"/>
-      <c r="C5156" s="32"/>
+      <c r="C5156" s="35"/>
     </row>
     <row r="5157" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5157" s="3">
@@ -36977,7 +36977,7 @@
       <c r="A5266" s="25">
         <v>5.2</v>
       </c>
-      <c r="B5266" s="35" t="s">
+      <c r="B5266" s="34" t="s">
         <v>342</v>
       </c>
       <c r="C5266" s="11" t="s">
@@ -36986,7 +36986,7 @@
     </row>
     <row r="5267" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5267" s="25"/>
-      <c r="B5267" s="35"/>
+      <c r="B5267" s="34"/>
       <c r="C5267" s="11"/>
     </row>
     <row r="5268" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -36994,14 +36994,14 @@
         <v>6.1</v>
       </c>
       <c r="B5268" s="7"/>
-      <c r="C5268" s="32" t="s">
+      <c r="C5268" s="35" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="5269" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5269" s="3"/>
       <c r="B5269" s="7"/>
-      <c r="C5269" s="32"/>
+      <c r="C5269" s="35"/>
     </row>
     <row r="5270" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5270" s="3">
@@ -37244,10 +37244,10 @@
     </row>
     <row r="5427" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5427" s="17"/>
-      <c r="B5427" s="33" t="s">
+      <c r="B5427" s="32" t="s">
         <v>166</v>
       </c>
-      <c r="C5427" s="34"/>
+      <c r="C5427" s="33"/>
     </row>
     <row r="5428" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5428" s="5" t="s">
@@ -37511,7 +37511,7 @@
       <c r="A5502" s="25">
         <v>5.2</v>
       </c>
-      <c r="B5502" s="35" t="s">
+      <c r="B5502" s="34" t="s">
         <v>342</v>
       </c>
       <c r="C5502" s="11" t="s">
@@ -37520,7 +37520,7 @@
     </row>
     <row r="5503" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5503" s="25"/>
-      <c r="B5503" s="35"/>
+      <c r="B5503" s="34"/>
       <c r="C5503" s="11"/>
     </row>
     <row r="5504" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -37528,14 +37528,14 @@
         <v>6.1</v>
       </c>
       <c r="B5504" s="7"/>
-      <c r="C5504" s="32" t="s">
+      <c r="C5504" s="35" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="5505" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5505" s="3"/>
       <c r="B5505" s="7"/>
-      <c r="C5505" s="32"/>
+      <c r="C5505" s="35"/>
     </row>
     <row r="5506" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5506" s="3">
@@ -37568,10 +37568,10 @@
     </row>
     <row r="5545" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5545" s="17"/>
-      <c r="B5545" s="33" t="s">
+      <c r="B5545" s="32" t="s">
         <v>153</v>
       </c>
-      <c r="C5545" s="34"/>
+      <c r="C5545" s="33"/>
     </row>
     <row r="5546" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5546" s="5" t="s">
@@ -37694,7 +37694,7 @@
       <c r="A5559" s="23">
         <v>5.2</v>
       </c>
-      <c r="B5559" s="35" t="s">
+      <c r="B5559" s="34" t="s">
         <v>342</v>
       </c>
       <c r="C5559" s="11" t="s">
@@ -37703,7 +37703,7 @@
     </row>
     <row r="5560" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5560" s="23"/>
-      <c r="B5560" s="35"/>
+      <c r="B5560" s="34"/>
       <c r="C5560" s="11"/>
     </row>
     <row r="5561" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -37711,19 +37711,19 @@
         <v>6.1</v>
       </c>
       <c r="B5561" s="7"/>
-      <c r="C5561" s="32" t="s">
+      <c r="C5561" s="35" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="5562" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5562" s="3"/>
       <c r="B5562" s="7"/>
-      <c r="C5562" s="32"/>
+      <c r="C5562" s="35"/>
     </row>
     <row r="5563" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5563" s="3"/>
       <c r="B5563" s="7"/>
-      <c r="C5563" s="32"/>
+      <c r="C5563" s="35"/>
     </row>
     <row r="5564" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5564" s="3">
@@ -37745,7 +37745,7 @@
       <c r="A5566" s="23">
         <v>7.2</v>
       </c>
-      <c r="B5566" s="35" t="s">
+      <c r="B5566" s="34" t="s">
         <v>344</v>
       </c>
       <c r="C5566" s="11" t="s">
@@ -37754,7 +37754,7 @@
     </row>
     <row r="5567" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5567" s="23"/>
-      <c r="B5567" s="35"/>
+      <c r="B5567" s="34"/>
       <c r="C5567" s="11"/>
     </row>
     <row r="5568" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -37813,10 +37813,10 @@
     </row>
     <row r="5604" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5604" s="17"/>
-      <c r="B5604" s="33" t="s">
+      <c r="B5604" s="32" t="s">
         <v>158</v>
       </c>
-      <c r="C5604" s="34"/>
+      <c r="C5604" s="33"/>
     </row>
     <row r="5605" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5605" s="5" t="s">
@@ -37945,7 +37945,7 @@
       <c r="A5618" s="25">
         <v>5.2</v>
       </c>
-      <c r="B5618" s="35" t="s">
+      <c r="B5618" s="34" t="s">
         <v>342</v>
       </c>
       <c r="C5618" s="11" t="s">
@@ -37954,7 +37954,7 @@
     </row>
     <row r="5619" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5619" s="25"/>
-      <c r="B5619" s="35"/>
+      <c r="B5619" s="34"/>
       <c r="C5619" s="11"/>
     </row>
     <row r="5620" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -37962,14 +37962,14 @@
         <v>6.1</v>
       </c>
       <c r="B5620" s="7"/>
-      <c r="C5620" s="32" t="s">
+      <c r="C5620" s="35" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="5621" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5621" s="3"/>
       <c r="B5621" s="7"/>
-      <c r="C5621" s="32"/>
+      <c r="C5621" s="35"/>
     </row>
     <row r="5622" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5622" s="3">
@@ -38002,10 +38002,10 @@
     </row>
     <row r="5663" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5663" s="17"/>
-      <c r="B5663" s="33" t="s">
+      <c r="B5663" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="C5663" s="34"/>
+      <c r="C5663" s="33"/>
     </row>
     <row r="5664" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5664" s="5" t="s">
@@ -38151,10 +38151,10 @@
     </row>
     <row r="5722" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5722" s="17"/>
-      <c r="B5722" s="33" t="s">
+      <c r="B5722" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="C5722" s="34"/>
+      <c r="C5722" s="33"/>
     </row>
     <row r="5723" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5723" s="5" t="s">
@@ -38561,10 +38561,10 @@
     </row>
     <row r="5781" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5781" s="17"/>
-      <c r="B5781" s="33" t="s">
+      <c r="B5781" s="32" t="s">
         <v>369</v>
       </c>
-      <c r="C5781" s="34"/>
+      <c r="C5781" s="33"/>
     </row>
     <row r="5782" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5782" s="5" t="s">
@@ -39679,19 +39679,19 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B6028" s="7"/>
-      <c r="C6028" s="32" t="s">
+      <c r="C6028" s="35" t="s">
         <v>325</v>
       </c>
     </row>
     <row r="6029" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6029" s="3"/>
       <c r="B6029" s="7"/>
-      <c r="C6029" s="32"/>
+      <c r="C6029" s="35"/>
     </row>
     <row r="6030" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6030" s="3"/>
       <c r="B6030" s="7"/>
-      <c r="C6030" s="32"/>
+      <c r="C6030" s="35"/>
     </row>
     <row r="6031" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6031" s="3">
@@ -39776,10 +39776,10 @@
     </row>
     <row r="6076" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6076" s="17"/>
-      <c r="B6076" s="33" t="s">
+      <c r="B6076" s="32" t="s">
         <v>87</v>
       </c>
-      <c r="C6076" s="34"/>
+      <c r="C6076" s="33"/>
     </row>
     <row r="6077" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6077" s="5" t="s">
@@ -39924,7 +39924,7 @@
       <c r="A6092" s="25">
         <v>7.2</v>
       </c>
-      <c r="B6092" s="35" t="s">
+      <c r="B6092" s="34" t="s">
         <v>342</v>
       </c>
       <c r="C6092" s="11" t="s">
@@ -39933,7 +39933,7 @@
     </row>
     <row r="6093" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6093" s="25"/>
-      <c r="B6093" s="35"/>
+      <c r="B6093" s="34"/>
       <c r="C6093" s="11"/>
     </row>
     <row r="6094" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -40293,14 +40293,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B6146" s="7"/>
-      <c r="C6146" s="32" t="s">
+      <c r="C6146" s="35" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="6147" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6147" s="3"/>
       <c r="B6147" s="7"/>
-      <c r="C6147" s="32"/>
+      <c r="C6147" s="35"/>
     </row>
     <row r="6148" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6148" s="3">
@@ -40709,19 +40709,19 @@
         <v>2.1</v>
       </c>
       <c r="B6258" s="7"/>
-      <c r="C6258" s="32" t="s">
+      <c r="C6258" s="35" t="s">
         <v>331</v>
       </c>
     </row>
     <row r="6259" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6259" s="3"/>
       <c r="B6259" s="7"/>
-      <c r="C6259" s="32"/>
+      <c r="C6259" s="35"/>
     </row>
     <row r="6260" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6260" s="3"/>
       <c r="B6260" s="7"/>
-      <c r="C6260" s="32"/>
+      <c r="C6260" s="35"/>
     </row>
     <row r="6261" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6261" s="3">
@@ -40905,10 +40905,10 @@
     </row>
     <row r="6371" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6371" s="17"/>
-      <c r="B6371" s="33" t="s">
+      <c r="B6371" s="32" t="s">
         <v>341</v>
       </c>
-      <c r="C6371" s="34"/>
+      <c r="C6371" s="33"/>
     </row>
     <row r="6372" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6372" s="5" t="s">
@@ -41148,7 +41148,7 @@
       <c r="A6440" s="25">
         <v>4.2</v>
       </c>
-      <c r="B6440" s="35" t="s">
+      <c r="B6440" s="34" t="s">
         <v>514</v>
       </c>
       <c r="C6440" s="11" t="s">
@@ -41157,7 +41157,7 @@
     </row>
     <row r="6441" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6441" s="25"/>
-      <c r="B6441" s="35"/>
+      <c r="B6441" s="34"/>
       <c r="C6441" s="11"/>
     </row>
     <row r="6442" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -41417,10 +41417,10 @@
     </row>
     <row r="6489" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6489" s="17"/>
-      <c r="B6489" s="33" t="s">
+      <c r="B6489" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="C6489" s="34"/>
+      <c r="C6489" s="33"/>
     </row>
     <row r="6490" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6490" s="5" t="s">
@@ -41515,7 +41515,7 @@
       <c r="A6499" s="23">
         <v>4.2</v>
       </c>
-      <c r="B6499" s="35" t="s">
+      <c r="B6499" s="34" t="s">
         <v>514</v>
       </c>
       <c r="C6499" s="11" t="s">
@@ -41524,7 +41524,7 @@
     </row>
     <row r="6500" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6500" s="23"/>
-      <c r="B6500" s="35"/>
+      <c r="B6500" s="34"/>
       <c r="C6500" s="11"/>
     </row>
     <row r="6501" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -41532,19 +41532,19 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B6501" s="7"/>
-      <c r="C6501" s="32" t="s">
+      <c r="C6501" s="35" t="s">
         <v>325</v>
       </c>
     </row>
     <row r="6502" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6502" s="3"/>
       <c r="B6502" s="7"/>
-      <c r="C6502" s="32"/>
+      <c r="C6502" s="35"/>
     </row>
     <row r="6503" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6503" s="3"/>
       <c r="B6503" s="7"/>
-      <c r="C6503" s="32"/>
+      <c r="C6503" s="35"/>
     </row>
     <row r="6504" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6504" s="3">
@@ -41566,7 +41566,7 @@
       <c r="A6506" s="23">
         <v>6.2</v>
       </c>
-      <c r="B6506" s="35" t="s">
+      <c r="B6506" s="34" t="s">
         <v>515</v>
       </c>
       <c r="C6506" s="8" t="s">
@@ -41575,7 +41575,7 @@
     </row>
     <row r="6507" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6507" s="23"/>
-      <c r="B6507" s="35"/>
+      <c r="B6507" s="34"/>
       <c r="C6507" s="8"/>
     </row>
     <row r="6508" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -41634,10 +41634,10 @@
     </row>
     <row r="6548" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6548" s="17"/>
-      <c r="B6548" s="33" t="s">
+      <c r="B6548" s="32" t="s">
         <v>108</v>
       </c>
-      <c r="C6548" s="34"/>
+      <c r="C6548" s="33"/>
     </row>
     <row r="6549" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6549" s="5" t="s">
@@ -41752,7 +41752,7 @@
       <c r="A6560" s="25">
         <v>5.2</v>
       </c>
-      <c r="B6560" s="35" t="s">
+      <c r="B6560" s="34" t="s">
         <v>343</v>
       </c>
       <c r="C6560" s="11" t="s">
@@ -41761,7 +41761,7 @@
     </row>
     <row r="6561" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6561" s="25"/>
-      <c r="B6561" s="35"/>
+      <c r="B6561" s="34"/>
       <c r="C6561" s="11"/>
     </row>
     <row r="6562" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -42126,10 +42126,10 @@
     </row>
     <row r="6666" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6666" s="17"/>
-      <c r="B6666" s="33" t="s">
+      <c r="B6666" s="32" t="s">
         <v>122</v>
       </c>
-      <c r="C6666" s="34"/>
+      <c r="C6666" s="33"/>
     </row>
     <row r="6667" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6667" s="5" t="s">
@@ -42300,7 +42300,7 @@
       <c r="A6686" s="25">
         <v>7.2</v>
       </c>
-      <c r="B6686" s="35" t="s">
+      <c r="B6686" s="34" t="s">
         <v>342</v>
       </c>
       <c r="C6686" s="8" t="s">
@@ -42309,7 +42309,7 @@
     </row>
     <row r="6687" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6687" s="25"/>
-      <c r="B6687" s="35"/>
+      <c r="B6687" s="34"/>
       <c r="C6687" s="8"/>
     </row>
     <row r="6688" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -42963,10 +42963,10 @@
     </row>
     <row r="6784" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6784" s="17"/>
-      <c r="B6784" s="33" t="s">
+      <c r="B6784" s="32" t="s">
         <v>127</v>
       </c>
-      <c r="C6784" s="34"/>
+      <c r="C6784" s="33"/>
     </row>
     <row r="6785" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6785" s="5" t="s">
@@ -43121,7 +43121,7 @@
       <c r="A6802" s="25">
         <v>7.2</v>
       </c>
-      <c r="B6802" s="35" t="s">
+      <c r="B6802" s="34" t="s">
         <v>342</v>
       </c>
       <c r="C6802" s="11" t="s">
@@ -43130,7 +43130,7 @@
     </row>
     <row r="6803" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6803" s="25"/>
-      <c r="B6803" s="35"/>
+      <c r="B6803" s="34"/>
       <c r="C6803" s="11"/>
     </row>
     <row r="6804" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -43915,10 +43915,10 @@
     </row>
     <row r="6961" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6961" s="17"/>
-      <c r="B6961" s="33" t="s">
+      <c r="B6961" s="32" t="s">
         <v>223</v>
       </c>
-      <c r="C6961" s="34"/>
+      <c r="C6961" s="33"/>
     </row>
     <row r="6962" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6962" s="5" t="s">
@@ -44035,19 +44035,19 @@
         <v>6.1</v>
       </c>
       <c r="B6974" s="7"/>
-      <c r="C6974" s="32" t="s">
+      <c r="C6974" s="35" t="s">
         <v>325</v>
       </c>
     </row>
     <row r="6975" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6975" s="3"/>
       <c r="B6975" s="7"/>
-      <c r="C6975" s="32"/>
+      <c r="C6975" s="35"/>
     </row>
     <row r="6976" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6976" s="3"/>
       <c r="B6976" s="7"/>
-      <c r="C6976" s="32"/>
+      <c r="C6976" s="35"/>
     </row>
     <row r="6977" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6977" s="3">
@@ -44132,10 +44132,10 @@
     </row>
     <row r="7020" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7020" s="17"/>
-      <c r="B7020" s="33" t="s">
+      <c r="B7020" s="32" t="s">
         <v>139</v>
       </c>
-      <c r="C7020" s="34"/>
+      <c r="C7020" s="33"/>
     </row>
     <row r="7021" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7021" s="5" t="s">
@@ -44296,7 +44296,7 @@
       <c r="A7038" s="25">
         <v>7.2</v>
       </c>
-      <c r="B7038" s="35" t="s">
+      <c r="B7038" s="34" t="s">
         <v>342</v>
       </c>
       <c r="C7038" s="11" t="s">
@@ -44305,7 +44305,7 @@
     </row>
     <row r="7039" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7039" s="25"/>
-      <c r="B7039" s="35"/>
+      <c r="B7039" s="34"/>
       <c r="C7039" s="11"/>
     </row>
     <row r="7040" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -44792,7 +44792,7 @@
       <c r="A7154" s="25">
         <v>5.2</v>
       </c>
-      <c r="B7154" s="35" t="s">
+      <c r="B7154" s="34" t="s">
         <v>342</v>
       </c>
       <c r="C7154" s="11" t="s">
@@ -44801,7 +44801,7 @@
     </row>
     <row r="7155" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7155" s="25"/>
-      <c r="B7155" s="35"/>
+      <c r="B7155" s="34"/>
       <c r="C7155" s="11"/>
     </row>
     <row r="7156" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -45161,14 +45161,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B7208" s="7"/>
-      <c r="C7208" s="32" t="s">
+      <c r="C7208" s="35" t="s">
         <v>358</v>
       </c>
     </row>
     <row r="7209" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7209" s="3"/>
       <c r="B7209" s="7"/>
-      <c r="C7209" s="32"/>
+      <c r="C7209" s="35"/>
     </row>
     <row r="7210" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7210" s="3">
@@ -45288,10 +45288,10 @@
     </row>
     <row r="7315" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7315" s="17"/>
-      <c r="B7315" s="33" t="s">
+      <c r="B7315" s="32" t="s">
         <v>620</v>
       </c>
-      <c r="C7315" s="34"/>
+      <c r="C7315" s="33"/>
     </row>
     <row r="7316" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7316" s="5" t="s">
@@ -45587,7 +45587,7 @@
       <c r="A7390" s="25">
         <v>5.2</v>
       </c>
-      <c r="B7390" s="35" t="s">
+      <c r="B7390" s="34" t="s">
         <v>342</v>
       </c>
       <c r="C7390" s="11" t="s">
@@ -45596,7 +45596,7 @@
     </row>
     <row r="7391" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7391" s="25"/>
-      <c r="B7391" s="35"/>
+      <c r="B7391" s="34"/>
       <c r="C7391" s="11"/>
     </row>
     <row r="7392" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -45856,10 +45856,10 @@
     </row>
     <row r="7433" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7433" s="17"/>
-      <c r="B7433" s="33" t="s">
+      <c r="B7433" s="32" t="s">
         <v>153</v>
       </c>
-      <c r="C7433" s="34"/>
+      <c r="C7433" s="33"/>
     </row>
     <row r="7434" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7434" s="5" t="s">
@@ -45982,7 +45982,7 @@
       <c r="A7447" s="23">
         <v>5.2</v>
       </c>
-      <c r="B7447" s="35" t="s">
+      <c r="B7447" s="34" t="s">
         <v>342</v>
       </c>
       <c r="C7447" s="11" t="s">
@@ -45991,7 +45991,7 @@
     </row>
     <row r="7448" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7448" s="23"/>
-      <c r="B7448" s="35"/>
+      <c r="B7448" s="34"/>
       <c r="C7448" s="11"/>
     </row>
     <row r="7449" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -45999,19 +45999,19 @@
         <v>6.1</v>
       </c>
       <c r="B7449" s="7"/>
-      <c r="C7449" s="32" t="s">
+      <c r="C7449" s="35" t="s">
         <v>325</v>
       </c>
     </row>
     <row r="7450" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7450" s="3"/>
       <c r="B7450" s="7"/>
-      <c r="C7450" s="32"/>
+      <c r="C7450" s="35"/>
     </row>
     <row r="7451" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7451" s="3"/>
       <c r="B7451" s="7"/>
-      <c r="C7451" s="32"/>
+      <c r="C7451" s="35"/>
     </row>
     <row r="7452" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7452" s="3">
@@ -46033,7 +46033,7 @@
       <c r="A7454" s="23">
         <v>7.2</v>
       </c>
-      <c r="B7454" s="35" t="s">
+      <c r="B7454" s="34" t="s">
         <v>344</v>
       </c>
       <c r="C7454" s="11" t="s">
@@ -46042,7 +46042,7 @@
     </row>
     <row r="7455" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7455" s="23"/>
-      <c r="B7455" s="35"/>
+      <c r="B7455" s="34"/>
       <c r="C7455" s="11"/>
     </row>
     <row r="7456" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -46233,7 +46233,7 @@
       <c r="A7506" s="25">
         <v>5.2</v>
       </c>
-      <c r="B7506" s="35" t="s">
+      <c r="B7506" s="34" t="s">
         <v>342</v>
       </c>
       <c r="C7506" s="11" t="s">
@@ -46242,7 +46242,7 @@
     </row>
     <row r="7507" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7507" s="25"/>
-      <c r="B7507" s="35"/>
+      <c r="B7507" s="34"/>
       <c r="C7507" s="11"/>
     </row>
     <row r="7508" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -46607,10 +46607,10 @@
     </row>
     <row r="7610" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7610" s="17"/>
-      <c r="B7610" s="33" t="s">
+      <c r="B7610" s="32" t="s">
         <v>372</v>
       </c>
-      <c r="C7610" s="34"/>
+      <c r="C7610" s="33"/>
     </row>
     <row r="7611" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7611" s="5" t="s">
@@ -46807,10 +46807,10 @@
     </row>
     <row r="7669" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7669" s="17"/>
-      <c r="B7669" s="33" t="s">
+      <c r="B7669" s="32" t="s">
         <v>369</v>
       </c>
-      <c r="C7669" s="34"/>
+      <c r="C7669" s="33"/>
     </row>
     <row r="7670" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7670" s="5" t="s">
@@ -47636,7 +47636,7 @@
       <c r="A7980" s="25">
         <v>7.2</v>
       </c>
-      <c r="B7980" s="35" t="s">
+      <c r="B7980" s="34" t="s">
         <v>344</v>
       </c>
       <c r="C7980" s="11" t="s">
@@ -47645,7 +47645,7 @@
     </row>
     <row r="7981" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7981" s="25"/>
-      <c r="B7981" s="35"/>
+      <c r="B7981" s="34"/>
       <c r="C7981" s="11"/>
     </row>
     <row r="7982" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -47738,14 +47738,14 @@
         <v>2.1</v>
       </c>
       <c r="B8028" s="7"/>
-      <c r="C8028" s="32" t="s">
+      <c r="C8028" s="35" t="s">
         <v>394</v>
       </c>
     </row>
     <row r="8029" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8029" s="3"/>
       <c r="B8029" s="7"/>
-      <c r="C8029" s="32"/>
+      <c r="C8029" s="35"/>
     </row>
     <row r="8030" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8030" s="3">
@@ -47937,14 +47937,14 @@
         <v>2.1</v>
       </c>
       <c r="B8146" s="7"/>
-      <c r="C8146" s="32" t="s">
+      <c r="C8146" s="35" t="s">
         <v>398</v>
       </c>
     </row>
     <row r="8147" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8147" s="3"/>
       <c r="B8147" s="7"/>
-      <c r="C8147" s="32"/>
+      <c r="C8147" s="35"/>
     </row>
     <row r="8148" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8148" s="3">
@@ -48176,7 +48176,7 @@
       <c r="A8269" s="25">
         <v>4.2</v>
       </c>
-      <c r="B8269" s="35" t="s">
+      <c r="B8269" s="34" t="s">
         <v>515</v>
       </c>
       <c r="C8269" s="11" t="s">
@@ -48185,7 +48185,7 @@
     </row>
     <row r="8270" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8270" s="25"/>
-      <c r="B8270" s="35"/>
+      <c r="B8270" s="34"/>
       <c r="C8270" s="11"/>
     </row>
     <row r="8271" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -48324,7 +48324,7 @@
       <c r="A8328" s="25">
         <v>4.2</v>
       </c>
-      <c r="B8328" s="35" t="s">
+      <c r="B8328" s="34" t="s">
         <v>515</v>
       </c>
       <c r="C8328" s="11" t="s">
@@ -48333,7 +48333,7 @@
     </row>
     <row r="8329" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8329" s="25"/>
-      <c r="B8329" s="35"/>
+      <c r="B8329" s="34"/>
       <c r="C8329" s="11"/>
     </row>
     <row r="8330" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -48472,7 +48472,7 @@
       <c r="A8387" s="25">
         <v>4.2</v>
       </c>
-      <c r="B8387" s="35" t="s">
+      <c r="B8387" s="34" t="s">
         <v>515</v>
       </c>
       <c r="C8387" s="11" t="s">
@@ -48481,7 +48481,7 @@
     </row>
     <row r="8388" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8388" s="25"/>
-      <c r="B8388" s="35"/>
+      <c r="B8388" s="34"/>
       <c r="C8388" s="11"/>
     </row>
     <row r="8389" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -48790,10 +48790,10 @@
     </row>
     <row r="8554" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8554" s="17"/>
-      <c r="B8554" s="33" t="s">
+      <c r="B8554" s="32" t="s">
         <v>414</v>
       </c>
-      <c r="C8554" s="34"/>
+      <c r="C8554" s="33"/>
     </row>
     <row r="8555" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8555" s="5" t="s">
@@ -48952,7 +48952,7 @@
       <c r="A8572" s="25">
         <v>7.2</v>
       </c>
-      <c r="B8572" s="35" t="s">
+      <c r="B8572" s="34" t="s">
         <v>344</v>
       </c>
       <c r="C8572" s="11" t="s">
@@ -48961,7 +48961,7 @@
     </row>
     <row r="8573" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8573" s="25"/>
-      <c r="B8573" s="35"/>
+      <c r="B8573" s="34"/>
       <c r="C8573" s="11"/>
     </row>
     <row r="8574" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -49179,10 +49179,10 @@
     </row>
     <row r="8672" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8672" s="17"/>
-      <c r="B8672" s="33" t="s">
+      <c r="B8672" s="32" t="s">
         <v>418</v>
       </c>
-      <c r="C8672" s="34"/>
+      <c r="C8672" s="33"/>
     </row>
     <row r="8673" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8673" s="5" t="s">
@@ -49339,7 +49339,7 @@
       <c r="A8690" s="25">
         <v>7.2</v>
       </c>
-      <c r="B8690" s="35" t="s">
+      <c r="B8690" s="34" t="s">
         <v>344</v>
       </c>
       <c r="C8690" s="11" t="s">
@@ -49348,7 +49348,7 @@
     </row>
     <row r="8691" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8691" s="25"/>
-      <c r="B8691" s="35"/>
+      <c r="B8691" s="34"/>
       <c r="C8691" s="11"/>
     </row>
     <row r="8692" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -49848,10 +49848,10 @@
     </row>
     <row r="8908" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8908" s="17"/>
-      <c r="B8908" s="33" t="s">
+      <c r="B8908" s="32" t="s">
         <v>424</v>
       </c>
-      <c r="C8908" s="34"/>
+      <c r="C8908" s="33"/>
     </row>
     <row r="8909" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8909" s="5" t="s">
@@ -50012,7 +50012,7 @@
       <c r="A8926" s="25">
         <v>7.2</v>
       </c>
-      <c r="B8926" s="35" t="s">
+      <c r="B8926" s="34" t="s">
         <v>344</v>
       </c>
       <c r="C8926" s="11" t="s">
@@ -50021,7 +50021,7 @@
     </row>
     <row r="8927" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8927" s="25"/>
-      <c r="B8927" s="35"/>
+      <c r="B8927" s="34"/>
       <c r="C8927" s="11"/>
     </row>
     <row r="8928" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -50114,14 +50114,14 @@
         <v>2.1</v>
       </c>
       <c r="B8972" s="7"/>
-      <c r="C8972" s="32" t="s">
+      <c r="C8972" s="35" t="s">
         <v>426</v>
       </c>
     </row>
     <row r="8973" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8973" s="3"/>
       <c r="B8973" s="7"/>
-      <c r="C8973" s="32"/>
+      <c r="C8973" s="35"/>
     </row>
     <row r="8974" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8974" s="3">
@@ -50282,7 +50282,7 @@
       <c r="A9040" s="25">
         <v>5.2</v>
       </c>
-      <c r="B9040" s="35" t="s">
+      <c r="B9040" s="34" t="s">
         <v>344</v>
       </c>
       <c r="C9040" s="11" t="s">
@@ -50291,7 +50291,7 @@
     </row>
     <row r="9041" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9041" s="25"/>
-      <c r="B9041" s="35"/>
+      <c r="B9041" s="34"/>
       <c r="C9041" s="11"/>
     </row>
     <row r="9042" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -50471,14 +50471,14 @@
         <v>2.1</v>
       </c>
       <c r="B9149" s="7"/>
-      <c r="C9149" s="32" t="s">
+      <c r="C9149" s="35" t="s">
         <v>432</v>
       </c>
     </row>
     <row r="9150" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9150" s="3"/>
       <c r="B9150" s="7"/>
-      <c r="C9150" s="32"/>
+      <c r="C9150" s="35"/>
     </row>
     <row r="9151" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9151" s="3">
@@ -50609,7 +50609,7 @@
       <c r="A9213" s="25">
         <v>4.2</v>
       </c>
-      <c r="B9213" s="35" t="s">
+      <c r="B9213" s="34" t="s">
         <v>515</v>
       </c>
       <c r="C9213" s="11" t="s">
@@ -50618,7 +50618,7 @@
     </row>
     <row r="9214" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9214" s="25"/>
-      <c r="B9214" s="35"/>
+      <c r="B9214" s="34"/>
       <c r="C9214" s="11"/>
     </row>
     <row r="9215" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -50787,7 +50787,7 @@
       <c r="A9276" s="25">
         <v>5.2</v>
       </c>
-      <c r="B9276" s="35" t="s">
+      <c r="B9276" s="34" t="s">
         <v>344</v>
       </c>
       <c r="C9276" s="11" t="s">
@@ -50796,7 +50796,7 @@
     </row>
     <row r="9277" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9277" s="25"/>
-      <c r="B9277" s="35"/>
+      <c r="B9277" s="34"/>
       <c r="C9277" s="11"/>
     </row>
     <row r="9278" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -50965,7 +50965,7 @@
       <c r="A9335" s="25">
         <v>5.2</v>
       </c>
-      <c r="B9335" s="35" t="s">
+      <c r="B9335" s="34" t="s">
         <v>344</v>
       </c>
       <c r="C9335" s="11" t="s">
@@ -50974,7 +50974,7 @@
     </row>
     <row r="9336" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9336" s="25"/>
-      <c r="B9336" s="35"/>
+      <c r="B9336" s="34"/>
       <c r="C9336" s="11"/>
     </row>
     <row r="9337" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -51147,7 +51147,7 @@
       <c r="A9394" s="25">
         <v>5.2</v>
       </c>
-      <c r="B9394" s="35" t="s">
+      <c r="B9394" s="34" t="s">
         <v>344</v>
       </c>
       <c r="C9394" s="11" t="s">
@@ -51156,7 +51156,7 @@
     </row>
     <row r="9395" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9395" s="25"/>
-      <c r="B9395" s="35"/>
+      <c r="B9395" s="34"/>
       <c r="C9395" s="11"/>
     </row>
     <row r="9396" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -51269,14 +51269,14 @@
         <v>3.1</v>
       </c>
       <c r="B9446" s="7"/>
-      <c r="C9446" s="32" t="s">
+      <c r="C9446" s="35" t="s">
         <v>440</v>
       </c>
     </row>
     <row r="9447" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9447" s="3"/>
       <c r="B9447" s="7"/>
-      <c r="C9447" s="32"/>
+      <c r="C9447" s="35"/>
     </row>
     <row r="9448" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9448" s="3">
@@ -51309,10 +51309,10 @@
     </row>
     <row r="9498" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9498" s="17"/>
-      <c r="B9498" s="33" t="s">
+      <c r="B9498" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="C9498" s="34"/>
+      <c r="C9498" s="33"/>
     </row>
     <row r="9499" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9499" s="5" t="s">
@@ -51474,14 +51474,14 @@
         <v>8.1</v>
       </c>
       <c r="B9516" s="2"/>
-      <c r="C9516" s="32" t="s">
+      <c r="C9516" s="35" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="9517" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9517" s="3"/>
       <c r="B9517" s="2"/>
-      <c r="C9517" s="32"/>
+      <c r="C9517" s="35"/>
     </row>
     <row r="9518" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9518" s="3">
@@ -51586,14 +51586,14 @@
         <v>3.1</v>
       </c>
       <c r="B9564" s="7"/>
-      <c r="C9564" s="32" t="s">
+      <c r="C9564" s="35" t="s">
         <v>445</v>
       </c>
     </row>
     <row r="9565" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9565" s="3"/>
       <c r="B9565" s="7"/>
-      <c r="C9565" s="32"/>
+      <c r="C9565" s="35"/>
     </row>
     <row r="9566" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9566" s="3">
@@ -51730,14 +51730,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B9627" s="7"/>
-      <c r="C9627" s="32" t="s">
+      <c r="C9627" s="35" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="9628" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9628" s="3"/>
       <c r="B9628" s="7"/>
-      <c r="C9628" s="32"/>
+      <c r="C9628" s="35"/>
     </row>
     <row r="9629" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9629" s="3">
@@ -51876,14 +51876,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B9686" s="7"/>
-      <c r="C9686" s="32" t="s">
+      <c r="C9686" s="35" t="s">
         <v>448</v>
       </c>
     </row>
     <row r="9687" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9687" s="3"/>
       <c r="B9687" s="7"/>
-      <c r="C9687" s="32"/>
+      <c r="C9687" s="35"/>
     </row>
     <row r="9688" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9688" s="3">
@@ -52022,14 +52022,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B9745" s="7"/>
-      <c r="C9745" s="32" t="s">
+      <c r="C9745" s="35" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="9746" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9746" s="3"/>
       <c r="B9746" s="7"/>
-      <c r="C9746" s="32"/>
+      <c r="C9746" s="35"/>
     </row>
     <row r="9747" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9747" s="3">
@@ -52168,14 +52168,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B9804" s="7"/>
-      <c r="C9804" s="32" t="s">
+      <c r="C9804" s="35" t="s">
         <v>451</v>
       </c>
     </row>
     <row r="9805" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9805" s="3"/>
       <c r="B9805" s="7"/>
-      <c r="C9805" s="32"/>
+      <c r="C9805" s="35"/>
     </row>
     <row r="9806" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9806" s="3">
@@ -52356,7 +52356,7 @@
       <c r="A9868" s="25">
         <v>7.2</v>
       </c>
-      <c r="B9868" s="35" t="s">
+      <c r="B9868" s="34" t="s">
         <v>342</v>
       </c>
       <c r="C9868" s="11" t="s">
@@ -52365,7 +52365,7 @@
     </row>
     <row r="9869" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9869" s="25"/>
-      <c r="B9869" s="35"/>
+      <c r="B9869" s="34"/>
       <c r="C9869" s="11"/>
     </row>
     <row r="9870" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -52373,14 +52373,14 @@
         <v>8.1</v>
       </c>
       <c r="B9870" s="7"/>
-      <c r="C9870" s="32" t="s">
+      <c r="C9870" s="35" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="9871" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9871" s="3"/>
       <c r="B9871" s="7"/>
-      <c r="C9871" s="32"/>
+      <c r="C9871" s="35"/>
     </row>
     <row r="9872" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9872" s="3">
@@ -52465,14 +52465,14 @@
         <v>2.1</v>
       </c>
       <c r="B9916" s="7"/>
-      <c r="C9916" s="32" t="s">
+      <c r="C9916" s="35" t="s">
         <v>454</v>
       </c>
     </row>
     <row r="9917" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9917" s="3"/>
       <c r="B9917" s="7"/>
-      <c r="C9917" s="32"/>
+      <c r="C9917" s="35"/>
     </row>
     <row r="9918" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9918" s="3">
@@ -52577,14 +52577,14 @@
         <v>3.1</v>
       </c>
       <c r="B9977" s="7"/>
-      <c r="C9977" s="32" t="s">
+      <c r="C9977" s="35" t="s">
         <v>456</v>
       </c>
     </row>
     <row r="9978" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9978" s="3"/>
       <c r="B9978" s="7"/>
-      <c r="C9978" s="32"/>
+      <c r="C9978" s="35"/>
     </row>
     <row r="9979" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9979" s="3">
@@ -52669,14 +52669,14 @@
         <v>2.1</v>
       </c>
       <c r="B10034" s="7"/>
-      <c r="C10034" s="32" t="s">
+      <c r="C10034" s="35" t="s">
         <v>458</v>
       </c>
     </row>
     <row r="10035" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10035" s="3"/>
       <c r="B10035" s="7"/>
-      <c r="C10035" s="32"/>
+      <c r="C10035" s="35"/>
     </row>
     <row r="10036" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10036" s="3">
@@ -52924,7 +52924,7 @@
       <c r="A10157" s="25">
         <v>4.2</v>
       </c>
-      <c r="B10157" s="35" t="s">
+      <c r="B10157" s="34" t="s">
         <v>514</v>
       </c>
       <c r="C10157" s="11" t="s">
@@ -52933,7 +52933,7 @@
     </row>
     <row r="10158" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10158" s="25"/>
-      <c r="B10158" s="35"/>
+      <c r="B10158" s="34"/>
       <c r="C10158" s="11"/>
     </row>
     <row r="10159" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -52941,14 +52941,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B10159" s="7"/>
-      <c r="C10159" s="32" t="s">
+      <c r="C10159" s="35" t="s">
         <v>448</v>
       </c>
     </row>
     <row r="10160" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10160" s="3"/>
       <c r="B10160" s="7"/>
-      <c r="C10160" s="32"/>
+      <c r="C10160" s="35"/>
     </row>
     <row r="10161" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10161" s="3">
@@ -53079,7 +53079,7 @@
       <c r="A10216" s="25">
         <v>4.2</v>
       </c>
-      <c r="B10216" s="35" t="s">
+      <c r="B10216" s="34" t="s">
         <v>514</v>
       </c>
       <c r="C10216" s="11" t="s">
@@ -53088,7 +53088,7 @@
     </row>
     <row r="10217" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10217" s="25"/>
-      <c r="B10217" s="35"/>
+      <c r="B10217" s="34"/>
       <c r="C10217" s="11"/>
     </row>
     <row r="10218" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -53096,14 +53096,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B10218" s="7"/>
-      <c r="C10218" s="32" t="s">
+      <c r="C10218" s="35" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="10219" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10219" s="3"/>
       <c r="B10219" s="7"/>
-      <c r="C10219" s="32"/>
+      <c r="C10219" s="35"/>
     </row>
     <row r="10220" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10220" s="3">
@@ -53234,7 +53234,7 @@
       <c r="A10275" s="25">
         <v>4.2</v>
       </c>
-      <c r="B10275" s="35" t="s">
+      <c r="B10275" s="34" t="s">
         <v>514</v>
       </c>
       <c r="C10275" s="11" t="s">
@@ -53243,7 +53243,7 @@
     </row>
     <row r="10276" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10276" s="25"/>
-      <c r="B10276" s="35"/>
+      <c r="B10276" s="34"/>
       <c r="C10276" s="11"/>
     </row>
     <row r="10277" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -53251,14 +53251,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B10277" s="7"/>
-      <c r="C10277" s="32" t="s">
+      <c r="C10277" s="35" t="s">
         <v>451</v>
       </c>
     </row>
     <row r="10278" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10278" s="3"/>
       <c r="B10278" s="7"/>
-      <c r="C10278" s="32"/>
+      <c r="C10278" s="35"/>
     </row>
     <row r="10279" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10279" s="3">
@@ -53409,7 +53409,7 @@
       <c r="A10336" s="25">
         <v>5.2</v>
       </c>
-      <c r="B10336" s="35" t="s">
+      <c r="B10336" s="34" t="s">
         <v>343</v>
       </c>
       <c r="C10336" s="11" t="s">
@@ -53418,7 +53418,7 @@
     </row>
     <row r="10337" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10337" s="25"/>
-      <c r="B10337" s="35"/>
+      <c r="B10337" s="34"/>
       <c r="C10337" s="11"/>
     </row>
     <row r="10338" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -53426,14 +53426,14 @@
         <v>6.1</v>
       </c>
       <c r="B10338" s="7"/>
-      <c r="C10338" s="32" t="s">
+      <c r="C10338" s="35" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="10339" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10339" s="3"/>
       <c r="B10339" s="7"/>
-      <c r="C10339" s="32"/>
+      <c r="C10339" s="35"/>
     </row>
     <row r="10340" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10340" s="3">
@@ -53571,10 +53571,10 @@
     </row>
     <row r="10442" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10442" s="17"/>
-      <c r="B10442" s="33" t="s">
+      <c r="B10442" s="32" t="s">
         <v>122</v>
       </c>
-      <c r="C10442" s="34"/>
+      <c r="C10442" s="33"/>
     </row>
     <row r="10443" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10443" s="5" t="s">
@@ -53745,7 +53745,7 @@
       <c r="A10462" s="25">
         <v>7.2</v>
       </c>
-      <c r="B10462" s="35" t="s">
+      <c r="B10462" s="34" t="s">
         <v>342</v>
       </c>
       <c r="C10462" s="11" t="s">
@@ -53754,7 +53754,7 @@
     </row>
     <row r="10463" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10463" s="25"/>
-      <c r="B10463" s="35"/>
+      <c r="B10463" s="34"/>
       <c r="C10463" s="11"/>
     </row>
     <row r="10464" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -53762,14 +53762,14 @@
         <v>8.1</v>
       </c>
       <c r="B10464" s="7"/>
-      <c r="C10464" s="32" t="s">
+      <c r="C10464" s="35" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="10465" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10465" s="3"/>
       <c r="B10465" s="7"/>
-      <c r="C10465" s="32"/>
+      <c r="C10465" s="35"/>
     </row>
     <row r="10466" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10466" s="3">
@@ -53944,14 +53944,14 @@
         <v>7.1</v>
       </c>
       <c r="B10516" s="7"/>
-      <c r="C10516" s="32" t="s">
+      <c r="C10516" s="35" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="10517" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10517" s="3"/>
       <c r="B10517" s="7"/>
-      <c r="C10517" s="32"/>
+      <c r="C10517" s="35"/>
     </row>
     <row r="10518" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10518" s="3">
@@ -53984,10 +53984,10 @@
     </row>
     <row r="10560" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10560" s="17"/>
-      <c r="B10560" s="33" t="s">
+      <c r="B10560" s="32" t="s">
         <v>127</v>
       </c>
-      <c r="C10560" s="34"/>
+      <c r="C10560" s="33"/>
     </row>
     <row r="10561" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10561" s="5" t="s">
@@ -54142,7 +54142,7 @@
       <c r="A10578" s="25">
         <v>7.2</v>
       </c>
-      <c r="B10578" s="35" t="s">
+      <c r="B10578" s="34" t="s">
         <v>342</v>
       </c>
       <c r="C10578" s="11" t="s">
@@ -54151,7 +54151,7 @@
     </row>
     <row r="10579" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10579" s="25"/>
-      <c r="B10579" s="35"/>
+      <c r="B10579" s="34"/>
       <c r="C10579" s="11"/>
     </row>
     <row r="10580" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -54159,14 +54159,14 @@
         <v>8.1</v>
       </c>
       <c r="B10580" s="7"/>
-      <c r="C10580" s="32" t="s">
+      <c r="C10580" s="35" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="10581" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10581" s="3"/>
       <c r="B10581" s="7"/>
-      <c r="C10581" s="32"/>
+      <c r="C10581" s="35"/>
     </row>
     <row r="10582" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10582" s="3">
@@ -54319,14 +54319,14 @@
         <v>6.1</v>
       </c>
       <c r="B10632" s="7"/>
-      <c r="C10632" s="32" t="s">
+      <c r="C10632" s="35" t="s">
         <v>448</v>
       </c>
     </row>
     <row r="10633" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10633" s="3"/>
       <c r="B10633" s="7"/>
-      <c r="C10633" s="32"/>
+      <c r="C10633" s="35"/>
     </row>
     <row r="10634" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10634" s="3">
@@ -54479,14 +54479,14 @@
         <v>6.1</v>
       </c>
       <c r="B10691" s="7"/>
-      <c r="C10691" s="32" t="s">
+      <c r="C10691" s="35" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="10692" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10692" s="3"/>
       <c r="B10692" s="7"/>
-      <c r="C10692" s="32"/>
+      <c r="C10692" s="35"/>
     </row>
     <row r="10693" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10693" s="3">
@@ -54639,14 +54639,14 @@
         <v>6.1</v>
       </c>
       <c r="B10750" s="7"/>
-      <c r="C10750" s="32" t="s">
+      <c r="C10750" s="35" t="s">
         <v>451</v>
       </c>
     </row>
     <row r="10751" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10751" s="3"/>
       <c r="B10751" s="7"/>
-      <c r="C10751" s="32"/>
+      <c r="C10751" s="35"/>
     </row>
     <row r="10752" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10752" s="3">
@@ -54679,10 +54679,10 @@
     </row>
     <row r="10796" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10796" s="17"/>
-      <c r="B10796" s="33" t="s">
+      <c r="B10796" s="32" t="s">
         <v>139</v>
       </c>
-      <c r="C10796" s="34"/>
+      <c r="C10796" s="33"/>
     </row>
     <row r="10797" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10797" s="5" t="s">
@@ -54843,7 +54843,7 @@
       <c r="A10814" s="25">
         <v>7.2</v>
       </c>
-      <c r="B10814" s="35" t="s">
+      <c r="B10814" s="34" t="s">
         <v>342</v>
       </c>
       <c r="C10814" s="8" t="s">
@@ -54852,7 +54852,7 @@
     </row>
     <row r="10815" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10815" s="25"/>
-      <c r="B10815" s="35"/>
+      <c r="B10815" s="34"/>
       <c r="C10815" s="8"/>
     </row>
     <row r="10816" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -54860,14 +54860,14 @@
         <v>8.1</v>
       </c>
       <c r="B10816" s="7"/>
-      <c r="C10816" s="32" t="s">
+      <c r="C10816" s="35" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="10817" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10817" s="3"/>
       <c r="B10817" s="7"/>
-      <c r="C10817" s="32"/>
+      <c r="C10817" s="35"/>
     </row>
     <row r="10818" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10818" s="3">
@@ -55127,7 +55127,7 @@
       <c r="A10930" s="25">
         <v>5.2</v>
       </c>
-      <c r="B10930" s="35" t="s">
+      <c r="B10930" s="34" t="s">
         <v>342</v>
       </c>
       <c r="C10930" s="11" t="s">
@@ -55136,7 +55136,7 @@
     </row>
     <row r="10931" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10931" s="25"/>
-      <c r="B10931" s="35"/>
+      <c r="B10931" s="34"/>
       <c r="C10931" s="11"/>
     </row>
     <row r="10932" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -55144,14 +55144,14 @@
         <v>6.1</v>
       </c>
       <c r="B10932" s="7"/>
-      <c r="C10932" s="32" t="s">
+      <c r="C10932" s="35" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="10933" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10933" s="3"/>
       <c r="B10933" s="7"/>
-      <c r="C10933" s="32"/>
+      <c r="C10933" s="35"/>
     </row>
     <row r="10934" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10934" s="3">
@@ -55236,14 +55236,14 @@
         <v>2.1</v>
       </c>
       <c r="B10978" s="7"/>
-      <c r="C10978" s="32" t="s">
+      <c r="C10978" s="35" t="s">
         <v>481</v>
       </c>
     </row>
     <row r="10979" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10979" s="3"/>
       <c r="B10979" s="7"/>
-      <c r="C10979" s="32"/>
+      <c r="C10979" s="35"/>
     </row>
     <row r="10980" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10980" s="3">
@@ -55328,14 +55328,14 @@
         <v>2.1</v>
       </c>
       <c r="B11037" s="7"/>
-      <c r="C11037" s="32" t="s">
+      <c r="C11037" s="35" t="s">
         <v>483</v>
       </c>
     </row>
     <row r="11038" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11038" s="3"/>
       <c r="B11038" s="7"/>
-      <c r="C11038" s="32"/>
+      <c r="C11038" s="35"/>
     </row>
     <row r="11039" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11039" s="3">
@@ -55508,7 +55508,7 @@
       <c r="A11107" s="25">
         <v>5.2</v>
       </c>
-      <c r="B11107" s="35" t="s">
+      <c r="B11107" s="34" t="s">
         <v>342</v>
       </c>
       <c r="C11107" s="11" t="s">
@@ -55517,7 +55517,7 @@
     </row>
     <row r="11108" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11108" s="25"/>
-      <c r="B11108" s="35"/>
+      <c r="B11108" s="34"/>
       <c r="C11108" s="11"/>
     </row>
     <row r="11109" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -55525,14 +55525,14 @@
         <v>6.1</v>
       </c>
       <c r="B11109" s="2"/>
-      <c r="C11109" s="32" t="s">
+      <c r="C11109" s="35" t="s">
         <v>448</v>
       </c>
     </row>
     <row r="11110" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11110" s="3"/>
       <c r="B11110" s="2"/>
-      <c r="C11110" s="32"/>
+      <c r="C11110" s="35"/>
     </row>
     <row r="11111" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11111" s="3">
@@ -55705,7 +55705,7 @@
       <c r="A11166" s="25">
         <v>5.2</v>
       </c>
-      <c r="B11166" s="35" t="s">
+      <c r="B11166" s="34" t="s">
         <v>342</v>
       </c>
       <c r="C11166" s="11" t="s">
@@ -55714,7 +55714,7 @@
     </row>
     <row r="11167" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11167" s="25"/>
-      <c r="B11167" s="35"/>
+      <c r="B11167" s="34"/>
       <c r="C11167" s="11"/>
     </row>
     <row r="11168" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -55722,14 +55722,14 @@
         <v>6.1</v>
       </c>
       <c r="B11168" s="2"/>
-      <c r="C11168" s="32" t="s">
+      <c r="C11168" s="35" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="11169" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11169" s="3"/>
       <c r="B11169" s="2"/>
-      <c r="C11169" s="32"/>
+      <c r="C11169" s="35"/>
     </row>
     <row r="11170" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11170" s="3">
@@ -55902,7 +55902,7 @@
       <c r="A11225" s="25">
         <v>5.2</v>
       </c>
-      <c r="B11225" s="35" t="s">
+      <c r="B11225" s="34" t="s">
         <v>342</v>
       </c>
       <c r="C11225" s="11" t="s">
@@ -55911,7 +55911,7 @@
     </row>
     <row r="11226" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11226" s="25"/>
-      <c r="B11226" s="35"/>
+      <c r="B11226" s="34"/>
       <c r="C11226" s="11"/>
     </row>
     <row r="11227" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -55919,14 +55919,14 @@
         <v>6.1</v>
       </c>
       <c r="B11227" s="2"/>
-      <c r="C11227" s="32" t="s">
+      <c r="C11227" s="35" t="s">
         <v>487</v>
       </c>
     </row>
     <row r="11228" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11228" s="3"/>
       <c r="B11228" s="2"/>
-      <c r="C11228" s="32"/>
+      <c r="C11228" s="35"/>
     </row>
     <row r="11229" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11229" s="3">
@@ -56091,7 +56091,7 @@
       <c r="A11282" s="25">
         <v>5.2</v>
       </c>
-      <c r="B11282" s="35" t="s">
+      <c r="B11282" s="34" t="s">
         <v>342</v>
       </c>
       <c r="C11282" s="11" t="s">
@@ -56100,7 +56100,7 @@
     </row>
     <row r="11283" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11283" s="25"/>
-      <c r="B11283" s="35"/>
+      <c r="B11283" s="34"/>
       <c r="C11283" s="11"/>
     </row>
     <row r="11284" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -56108,14 +56108,14 @@
         <v>6.1</v>
       </c>
       <c r="B11284" s="7"/>
-      <c r="C11284" s="32" t="s">
+      <c r="C11284" s="35" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="11285" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11285" s="3"/>
       <c r="B11285" s="7"/>
-      <c r="C11285" s="32"/>
+      <c r="C11285" s="35"/>
     </row>
     <row r="11286" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11286" s="3">
@@ -56220,19 +56220,19 @@
         <v>3.1</v>
       </c>
       <c r="B11334" s="7"/>
-      <c r="C11334" s="32" t="s">
+      <c r="C11334" s="35" t="s">
         <v>490</v>
       </c>
     </row>
     <row r="11335" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11335" s="3"/>
       <c r="B11335" s="7"/>
-      <c r="C11335" s="32"/>
+      <c r="C11335" s="35"/>
     </row>
     <row r="11336" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11336" s="3"/>
       <c r="B11336" s="7"/>
-      <c r="C11336" s="32"/>
+      <c r="C11336" s="35"/>
     </row>
     <row r="11337" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11337" s="3">
@@ -56265,10 +56265,10 @@
     </row>
     <row r="11386" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11386" s="17"/>
-      <c r="B11386" s="33" t="s">
+      <c r="B11386" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="C11386" s="34"/>
+      <c r="C11386" s="33"/>
     </row>
     <row r="11387" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11387" s="5" t="s">
@@ -56430,19 +56430,19 @@
         <v>8.1</v>
       </c>
       <c r="B11404" s="7"/>
-      <c r="C11404" s="32" t="s">
+      <c r="C11404" s="35" t="s">
         <v>492</v>
       </c>
     </row>
     <row r="11405" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11405" s="3"/>
       <c r="B11405" s="7"/>
-      <c r="C11405" s="32"/>
+      <c r="C11405" s="35"/>
     </row>
     <row r="11406" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11406" s="3"/>
       <c r="B11406" s="7"/>
-      <c r="C11406" s="32"/>
+      <c r="C11406" s="35"/>
     </row>
     <row r="11407" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11407" s="3">
@@ -56682,19 +56682,19 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B11515" s="7"/>
-      <c r="C11515" s="32" t="s">
+      <c r="C11515" s="35" t="s">
         <v>492</v>
       </c>
     </row>
     <row r="11516" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11516" s="3"/>
       <c r="B11516" s="7"/>
-      <c r="C11516" s="32"/>
+      <c r="C11516" s="35"/>
     </row>
     <row r="11517" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11517" s="3"/>
       <c r="B11517" s="7"/>
-      <c r="C11517" s="32"/>
+      <c r="C11517" s="35"/>
     </row>
     <row r="11518" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11518" s="3">
@@ -56833,19 +56833,19 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B11574" s="7"/>
-      <c r="C11574" s="32" t="s">
+      <c r="C11574" s="35" t="s">
         <v>497</v>
       </c>
     </row>
     <row r="11575" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11575" s="3"/>
       <c r="B11575" s="7"/>
-      <c r="C11575" s="32"/>
+      <c r="C11575" s="35"/>
     </row>
     <row r="11576" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11576" s="3"/>
       <c r="B11576" s="7"/>
-      <c r="C11576" s="32"/>
+      <c r="C11576" s="35"/>
     </row>
     <row r="11577" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11577" s="3">
@@ -56984,19 +56984,19 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B11633" s="7"/>
-      <c r="C11633" s="32" t="s">
+      <c r="C11633" s="35" t="s">
         <v>492</v>
       </c>
     </row>
     <row r="11634" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11634" s="3"/>
       <c r="B11634" s="7"/>
-      <c r="C11634" s="32"/>
+      <c r="C11634" s="35"/>
     </row>
     <row r="11635" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11635" s="3"/>
       <c r="B11635" s="7"/>
-      <c r="C11635" s="32"/>
+      <c r="C11635" s="35"/>
     </row>
     <row r="11636" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11636" s="3">
@@ -57029,10 +57029,10 @@
     </row>
     <row r="11681" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11681" s="17"/>
-      <c r="B11681" s="33" t="s">
+      <c r="B11681" s="32" t="s">
         <v>80</v>
       </c>
-      <c r="C11681" s="34"/>
+      <c r="C11681" s="33"/>
     </row>
     <row r="11682" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11682" s="5" t="s">
@@ -57135,14 +57135,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B11692" s="7"/>
-      <c r="C11692" s="32" t="s">
+      <c r="C11692" s="35" t="s">
         <v>624</v>
       </c>
     </row>
     <row r="11693" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11693" s="3"/>
       <c r="B11693" s="7"/>
-      <c r="C11693" s="32"/>
+      <c r="C11693" s="35"/>
     </row>
     <row r="11694" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11694" s="23">
@@ -57375,7 +57375,7 @@
       <c r="A11756" s="25">
         <v>7.2</v>
       </c>
-      <c r="B11756" s="35" t="s">
+      <c r="B11756" s="34" t="s">
         <v>342</v>
       </c>
       <c r="C11756" s="8" t="s">
@@ -57384,7 +57384,7 @@
     </row>
     <row r="11757" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11757" s="25"/>
-      <c r="B11757" s="35"/>
+      <c r="B11757" s="34"/>
       <c r="C11757" s="8"/>
     </row>
     <row r="11758" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -57392,19 +57392,19 @@
         <v>8.1</v>
       </c>
       <c r="B11758" s="7"/>
-      <c r="C11758" s="32" t="s">
+      <c r="C11758" s="35" t="s">
         <v>501</v>
       </c>
     </row>
     <row r="11759" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11759" s="3"/>
       <c r="B11759" s="7"/>
-      <c r="C11759" s="32"/>
+      <c r="C11759" s="35"/>
     </row>
     <row r="11760" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11760" s="3"/>
       <c r="B11760" s="7"/>
-      <c r="C11760" s="32"/>
+      <c r="C11760" s="35"/>
     </row>
     <row r="11761" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11761" s="3">
@@ -57489,14 +57489,14 @@
         <v>2.1</v>
       </c>
       <c r="B11804" s="7"/>
-      <c r="C11804" s="32" t="s">
+      <c r="C11804" s="35" t="s">
         <v>503</v>
       </c>
     </row>
     <row r="11805" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11805" s="3"/>
       <c r="B11805" s="7"/>
-      <c r="C11805" s="32"/>
+      <c r="C11805" s="35"/>
     </row>
     <row r="11806" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11806" s="3">
@@ -57601,19 +57601,19 @@
         <v>3.1</v>
       </c>
       <c r="B11865" s="7"/>
-      <c r="C11865" s="32" t="s">
+      <c r="C11865" s="35" t="s">
         <v>505</v>
       </c>
     </row>
     <row r="11866" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11866" s="3"/>
       <c r="B11866" s="7"/>
-      <c r="C11866" s="32"/>
+      <c r="C11866" s="35"/>
     </row>
     <row r="11867" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11867" s="3"/>
       <c r="B11867" s="7"/>
-      <c r="C11867" s="32"/>
+      <c r="C11867" s="35"/>
     </row>
     <row r="11868" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11868" s="3">
@@ -57698,14 +57698,14 @@
         <v>2.1</v>
       </c>
       <c r="B11922" s="7"/>
-      <c r="C11922" s="32" t="s">
+      <c r="C11922" s="35" t="s">
         <v>507</v>
       </c>
     </row>
     <row r="11923" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11923" s="3"/>
       <c r="B11923" s="7"/>
-      <c r="C11923" s="32"/>
+      <c r="C11923" s="35"/>
     </row>
     <row r="11924" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11924" s="3">
@@ -57926,7 +57926,7 @@
       <c r="A12045" s="25">
         <v>4.2</v>
       </c>
-      <c r="B12045" s="35" t="s">
+      <c r="B12045" s="34" t="s">
         <v>514</v>
       </c>
       <c r="C12045" s="11" t="s">
@@ -57935,7 +57935,7 @@
     </row>
     <row r="12046" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12046" s="25"/>
-      <c r="B12046" s="35"/>
+      <c r="B12046" s="34"/>
       <c r="C12046" s="11"/>
     </row>
     <row r="12047" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -57943,19 +57943,19 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B12047" s="7"/>
-      <c r="C12047" s="32" t="s">
+      <c r="C12047" s="35" t="s">
         <v>497</v>
       </c>
     </row>
     <row r="12048" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12048" s="3"/>
       <c r="B12048" s="7"/>
-      <c r="C12048" s="32"/>
+      <c r="C12048" s="35"/>
     </row>
     <row r="12049" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12049" s="3"/>
       <c r="B12049" s="7"/>
-      <c r="C12049" s="32"/>
+      <c r="C12049" s="35"/>
     </row>
     <row r="12050" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12050" s="3">
@@ -58086,7 +58086,7 @@
       <c r="A12104" s="25">
         <v>4.2</v>
       </c>
-      <c r="B12104" s="35" t="s">
+      <c r="B12104" s="34" t="s">
         <v>514</v>
       </c>
       <c r="C12104" s="11" t="s">
@@ -58095,7 +58095,7 @@
     </row>
     <row r="12105" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12105" s="25"/>
-      <c r="B12105" s="35"/>
+      <c r="B12105" s="34"/>
       <c r="C12105" s="11"/>
     </row>
     <row r="12106" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -58103,19 +58103,19 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B12106" s="7"/>
-      <c r="C12106" s="32" t="s">
+      <c r="C12106" s="35" t="s">
         <v>492</v>
       </c>
     </row>
     <row r="12107" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12107" s="3"/>
       <c r="B12107" s="7"/>
-      <c r="C12107" s="32"/>
+      <c r="C12107" s="35"/>
     </row>
     <row r="12108" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12108" s="3"/>
       <c r="B12108" s="7"/>
-      <c r="C12108" s="32"/>
+      <c r="C12108" s="35"/>
     </row>
     <row r="12109" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12109" s="3">
@@ -58148,10 +58148,10 @@
     </row>
     <row r="12153" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12153" s="17"/>
-      <c r="B12153" s="33" t="s">
+      <c r="B12153" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="C12153" s="34"/>
+      <c r="C12153" s="33"/>
     </row>
     <row r="12154" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12154" s="5" t="s">
@@ -58246,7 +58246,7 @@
       <c r="A12163" s="23">
         <v>4.2</v>
       </c>
-      <c r="B12163" s="35" t="s">
+      <c r="B12163" s="34" t="s">
         <v>514</v>
       </c>
       <c r="C12163" s="11" t="s">
@@ -58255,7 +58255,7 @@
     </row>
     <row r="12164" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12164" s="23"/>
-      <c r="B12164" s="35"/>
+      <c r="B12164" s="34"/>
       <c r="C12164" s="11"/>
     </row>
     <row r="12165" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -58263,14 +58263,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B12165" s="7"/>
-      <c r="C12165" s="32" t="s">
+      <c r="C12165" s="35" t="s">
         <v>624</v>
       </c>
     </row>
     <row r="12166" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12166" s="3"/>
       <c r="B12166" s="7"/>
-      <c r="C12166" s="32"/>
+      <c r="C12166" s="35"/>
     </row>
     <row r="12167" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12167" s="3">
@@ -58292,7 +58292,7 @@
       <c r="A12169" s="23">
         <v>6.2</v>
       </c>
-      <c r="B12169" s="35" t="s">
+      <c r="B12169" s="34" t="s">
         <v>515</v>
       </c>
       <c r="C12169" s="11" t="s">
@@ -58301,7 +58301,7 @@
     </row>
     <row r="12170" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12170" s="23"/>
-      <c r="B12170" s="35"/>
+      <c r="B12170" s="34"/>
       <c r="C12170" s="11"/>
     </row>
     <row r="12171" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -58478,7 +58478,7 @@
       <c r="A12224" s="25">
         <v>5.2</v>
       </c>
-      <c r="B12224" s="35" t="s">
+      <c r="B12224" s="34" t="s">
         <v>343</v>
       </c>
       <c r="C12224" s="8" t="s">
@@ -58487,7 +58487,7 @@
     </row>
     <row r="12225" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12225" s="25"/>
-      <c r="B12225" s="35"/>
+      <c r="B12225" s="34"/>
       <c r="C12225" s="8"/>
     </row>
     <row r="12226" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -58495,19 +58495,19 @@
         <v>6.1</v>
       </c>
       <c r="B12226" s="7"/>
-      <c r="C12226" s="32" t="s">
+      <c r="C12226" s="35" t="s">
         <v>492</v>
       </c>
     </row>
     <row r="12227" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12227" s="3"/>
       <c r="B12227" s="7"/>
-      <c r="C12227" s="32"/>
+      <c r="C12227" s="35"/>
     </row>
     <row r="12228" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12228" s="3"/>
       <c r="B12228" s="7"/>
-      <c r="C12228" s="32"/>
+      <c r="C12228" s="35"/>
     </row>
     <row r="12229" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12229" s="3">
@@ -58645,10 +58645,10 @@
     </row>
     <row r="12330" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12330" s="17"/>
-      <c r="B12330" s="33" t="s">
+      <c r="B12330" s="32" t="s">
         <v>122</v>
       </c>
-      <c r="C12330" s="34"/>
+      <c r="C12330" s="33"/>
     </row>
     <row r="12331" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12331" s="5" t="s">
@@ -58819,7 +58819,7 @@
       <c r="A12350" s="25">
         <v>7.2</v>
       </c>
-      <c r="B12350" s="35" t="s">
+      <c r="B12350" s="34" t="s">
         <v>342</v>
       </c>
       <c r="C12350" s="8" t="s">
@@ -58828,7 +58828,7 @@
     </row>
     <row r="12351" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12351" s="25"/>
-      <c r="B12351" s="35"/>
+      <c r="B12351" s="34"/>
       <c r="C12351" s="8"/>
     </row>
     <row r="12352" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -58836,19 +58836,19 @@
         <v>8.1</v>
       </c>
       <c r="B12352" s="7"/>
-      <c r="C12352" s="32" t="s">
+      <c r="C12352" s="35" t="s">
         <v>492</v>
       </c>
     </row>
     <row r="12353" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12353" s="3"/>
       <c r="B12353" s="7"/>
-      <c r="C12353" s="32"/>
+      <c r="C12353" s="35"/>
     </row>
     <row r="12354" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12354" s="3"/>
       <c r="B12354" s="7"/>
-      <c r="C12354" s="32"/>
+      <c r="C12354" s="35"/>
     </row>
     <row r="12355" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12355" s="3">
@@ -59023,19 +59023,19 @@
         <v>7.1</v>
       </c>
       <c r="B12404" s="7"/>
-      <c r="C12404" s="32" t="s">
+      <c r="C12404" s="35" t="s">
         <v>492</v>
       </c>
     </row>
     <row r="12405" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12405" s="3"/>
       <c r="B12405" s="7"/>
-      <c r="C12405" s="32"/>
+      <c r="C12405" s="35"/>
     </row>
     <row r="12406" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12406" s="3"/>
       <c r="B12406" s="7"/>
-      <c r="C12406" s="32"/>
+      <c r="C12406" s="35"/>
     </row>
     <row r="12407" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12407" s="3">
@@ -59068,10 +59068,10 @@
     </row>
     <row r="12448" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12448" s="17"/>
-      <c r="B12448" s="33" t="s">
+      <c r="B12448" s="32" t="s">
         <v>127</v>
       </c>
-      <c r="C12448" s="34"/>
+      <c r="C12448" s="33"/>
     </row>
     <row r="12449" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12449" s="5" t="s">
@@ -59226,7 +59226,7 @@
       <c r="A12466" s="25">
         <v>7.2</v>
       </c>
-      <c r="B12466" s="35" t="s">
+      <c r="B12466" s="34" t="s">
         <v>342</v>
       </c>
       <c r="C12466" s="8" t="s">
@@ -59235,7 +59235,7 @@
     </row>
     <row r="12467" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12467" s="25"/>
-      <c r="B12467" s="35"/>
+      <c r="B12467" s="34"/>
       <c r="C12467" s="8"/>
     </row>
     <row r="12468" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -59243,19 +59243,19 @@
         <v>8.1</v>
       </c>
       <c r="B12468" s="7"/>
-      <c r="C12468" s="32" t="s">
+      <c r="C12468" s="35" t="s">
         <v>492</v>
       </c>
     </row>
     <row r="12469" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12469" s="3"/>
       <c r="B12469" s="7"/>
-      <c r="C12469" s="32"/>
+      <c r="C12469" s="35"/>
     </row>
     <row r="12470" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12470" s="3"/>
       <c r="B12470" s="7"/>
-      <c r="C12470" s="32"/>
+      <c r="C12470" s="35"/>
     </row>
     <row r="12471" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12471" s="3">
@@ -59382,7 +59382,7 @@
       <c r="A12517" s="3">
         <v>4.2</v>
       </c>
-      <c r="B12517" s="32" t="s">
+      <c r="B12517" s="35" t="s">
         <v>537</v>
       </c>
       <c r="C12517" s="2" t="s">
@@ -59391,12 +59391,12 @@
     </row>
     <row r="12518" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12518" s="3"/>
-      <c r="B12518" s="32"/>
+      <c r="B12518" s="35"/>
       <c r="C12518" s="2"/>
     </row>
     <row r="12519" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12519" s="3"/>
-      <c r="B12519" s="32"/>
+      <c r="B12519" s="35"/>
       <c r="C12519" s="2"/>
     </row>
     <row r="12520" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -59595,19 +59595,19 @@
         <v>6.1</v>
       </c>
       <c r="B12579" s="7"/>
-      <c r="C12579" s="32" t="s">
+      <c r="C12579" s="35" t="s">
         <v>492</v>
       </c>
     </row>
     <row r="12580" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12580" s="3"/>
       <c r="B12580" s="7"/>
-      <c r="C12580" s="32"/>
+      <c r="C12580" s="35"/>
     </row>
     <row r="12581" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12581" s="3"/>
       <c r="B12581" s="7"/>
-      <c r="C12581" s="32"/>
+      <c r="C12581" s="35"/>
     </row>
     <row r="12582" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12582" s="3">
@@ -59760,14 +59760,14 @@
         <v>6.1</v>
       </c>
       <c r="B12638" s="7"/>
-      <c r="C12638" s="32" t="s">
+      <c r="C12638" s="35" t="s">
         <v>586</v>
       </c>
     </row>
     <row r="12639" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12639" s="3"/>
       <c r="B12639" s="7"/>
-      <c r="C12639" s="32"/>
+      <c r="C12639" s="35"/>
     </row>
     <row r="12640" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12640" s="3">
@@ -59852,10 +59852,10 @@
     </row>
     <row r="12684" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12684" s="17"/>
-      <c r="B12684" s="33" t="s">
+      <c r="B12684" s="32" t="s">
         <v>139</v>
       </c>
-      <c r="C12684" s="34"/>
+      <c r="C12684" s="33"/>
     </row>
     <row r="12685" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12685" s="5" t="s">
@@ -60016,7 +60016,7 @@
       <c r="A12702" s="25">
         <v>7.2</v>
       </c>
-      <c r="B12702" s="35" t="s">
+      <c r="B12702" s="34" t="s">
         <v>342</v>
       </c>
       <c r="C12702" s="11" t="s">
@@ -60025,7 +60025,7 @@
     </row>
     <row r="12703" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12703" s="25"/>
-      <c r="B12703" s="35"/>
+      <c r="B12703" s="34"/>
       <c r="C12703" s="11"/>
     </row>
     <row r="12704" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -60033,19 +60033,19 @@
         <v>8.1</v>
       </c>
       <c r="B12704" s="2"/>
-      <c r="C12704" s="32" t="s">
+      <c r="C12704" s="35" t="s">
         <v>492</v>
       </c>
     </row>
     <row r="12705" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12705" s="3"/>
       <c r="B12705" s="2"/>
-      <c r="C12705" s="32"/>
+      <c r="C12705" s="35"/>
     </row>
     <row r="12706" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12706" s="3"/>
       <c r="B12706" s="2"/>
-      <c r="C12706" s="32"/>
+      <c r="C12706" s="35"/>
     </row>
     <row r="12707" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12707" s="3">
@@ -60305,7 +60305,7 @@
       <c r="A12818" s="25">
         <v>5.2</v>
       </c>
-      <c r="B12818" s="35" t="s">
+      <c r="B12818" s="34" t="s">
         <v>544</v>
       </c>
       <c r="C12818" s="11" t="s">
@@ -60314,7 +60314,7 @@
     </row>
     <row r="12819" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12819" s="25"/>
-      <c r="B12819" s="35"/>
+      <c r="B12819" s="34"/>
       <c r="C12819" s="11"/>
     </row>
     <row r="12820" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -60322,19 +60322,19 @@
         <v>6.1</v>
       </c>
       <c r="B12820" s="7"/>
-      <c r="C12820" s="32" t="s">
+      <c r="C12820" s="35" t="s">
         <v>492</v>
       </c>
     </row>
     <row r="12821" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12821" s="3"/>
       <c r="B12821" s="7"/>
-      <c r="C12821" s="32"/>
+      <c r="C12821" s="35"/>
     </row>
     <row r="12822" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12822" s="3"/>
       <c r="B12822" s="7"/>
-      <c r="C12822" s="32"/>
+      <c r="C12822" s="35"/>
     </row>
     <row r="12823" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12823" s="3">
@@ -60699,7 +60699,7 @@
       <c r="A12991" s="24">
         <v>5.2</v>
       </c>
-      <c r="B12991" s="32" t="s">
+      <c r="B12991" s="35" t="s">
         <v>552</v>
       </c>
       <c r="C12991" s="2" t="s">
@@ -60708,12 +60708,12 @@
     </row>
     <row r="12992" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12992" s="24"/>
-      <c r="B12992" s="32"/>
+      <c r="B12992" s="35"/>
       <c r="C12992" s="2"/>
     </row>
     <row r="12993" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12993" s="24"/>
-      <c r="B12993" s="32"/>
+      <c r="B12993" s="35"/>
       <c r="C12993" s="2"/>
     </row>
     <row r="12994" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -60896,7 +60896,7 @@
       <c r="A13054" s="25">
         <v>5.2</v>
       </c>
-      <c r="B13054" s="35" t="s">
+      <c r="B13054" s="34" t="s">
         <v>342</v>
       </c>
       <c r="C13054" s="11" t="s">
@@ -60905,7 +60905,7 @@
     </row>
     <row r="13055" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13055" s="25"/>
-      <c r="B13055" s="35"/>
+      <c r="B13055" s="34"/>
       <c r="C13055" s="11"/>
     </row>
     <row r="13056" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -60913,19 +60913,19 @@
         <v>6.1</v>
       </c>
       <c r="B13056" s="2"/>
-      <c r="C13056" s="32" t="s">
+      <c r="C13056" s="35" t="s">
         <v>492</v>
       </c>
     </row>
     <row r="13057" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13057" s="3"/>
       <c r="B13057" s="2"/>
-      <c r="C13057" s="32"/>
+      <c r="C13057" s="35"/>
     </row>
     <row r="13058" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13058" s="3"/>
       <c r="B13058" s="2"/>
-      <c r="C13058" s="32"/>
+      <c r="C13058" s="35"/>
     </row>
     <row r="13059" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13059" s="3">
@@ -60958,10 +60958,10 @@
     </row>
     <row r="13097" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13097" s="17"/>
-      <c r="B13097" s="33" t="s">
+      <c r="B13097" s="32" t="s">
         <v>153</v>
       </c>
-      <c r="C13097" s="34"/>
+      <c r="C13097" s="33"/>
     </row>
     <row r="13098" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13098" s="5" t="s">
@@ -61084,7 +61084,7 @@
       <c r="A13111" s="23">
         <v>5.2</v>
       </c>
-      <c r="B13111" s="35" t="s">
+      <c r="B13111" s="34" t="s">
         <v>342</v>
       </c>
       <c r="C13111" s="11" t="s">
@@ -61093,7 +61093,7 @@
     </row>
     <row r="13112" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13112" s="23"/>
-      <c r="B13112" s="35"/>
+      <c r="B13112" s="34"/>
       <c r="C13112" s="11"/>
     </row>
     <row r="13113" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -61101,14 +61101,14 @@
         <v>6.1</v>
       </c>
       <c r="B13113" s="7"/>
-      <c r="C13113" s="32" t="s">
+      <c r="C13113" s="35" t="s">
         <v>624</v>
       </c>
     </row>
     <row r="13114" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13114" s="3"/>
       <c r="B13114" s="7"/>
-      <c r="C13114" s="32"/>
+      <c r="C13114" s="35"/>
     </row>
     <row r="13115" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13115" s="3">
@@ -61130,7 +61130,7 @@
       <c r="A13117" s="23">
         <v>7.2</v>
       </c>
-      <c r="B13117" s="35" t="s">
+      <c r="B13117" s="34" t="s">
         <v>344</v>
       </c>
       <c r="C13117" s="11" t="s">
@@ -61139,7 +61139,7 @@
     </row>
     <row r="13118" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13118" s="23"/>
-      <c r="B13118" s="35"/>
+      <c r="B13118" s="34"/>
       <c r="C13118" s="11"/>
     </row>
     <row r="13119" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -61330,7 +61330,7 @@
       <c r="A13170" s="25">
         <v>5.2</v>
       </c>
-      <c r="B13170" s="35" t="s">
+      <c r="B13170" s="34" t="s">
         <v>342</v>
       </c>
       <c r="C13170" s="11" t="s">
@@ -61339,7 +61339,7 @@
     </row>
     <row r="13171" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13171" s="25"/>
-      <c r="B13171" s="35"/>
+      <c r="B13171" s="34"/>
       <c r="C13171" s="11"/>
     </row>
     <row r="13172" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -61347,19 +61347,19 @@
         <v>6.1</v>
       </c>
       <c r="B13172" s="2"/>
-      <c r="C13172" s="32" t="s">
+      <c r="C13172" s="35" t="s">
         <v>492</v>
       </c>
     </row>
     <row r="13173" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13173" s="3"/>
       <c r="B13173" s="2"/>
-      <c r="C13173" s="32"/>
+      <c r="C13173" s="35"/>
     </row>
     <row r="13174" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13174" s="3"/>
       <c r="B13174" s="2"/>
-      <c r="C13174" s="32"/>
+      <c r="C13174" s="35"/>
     </row>
     <row r="13175" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13175" s="3">
@@ -61464,19 +61464,19 @@
         <v>3.1</v>
       </c>
       <c r="B13222" s="7"/>
-      <c r="C13222" s="32" t="s">
+      <c r="C13222" s="35" t="s">
         <v>558</v>
       </c>
     </row>
     <row r="13223" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13223" s="3"/>
       <c r="B13223" s="7"/>
-      <c r="C13223" s="32"/>
+      <c r="C13223" s="35"/>
     </row>
     <row r="13224" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13224" s="3"/>
       <c r="B13224" s="7"/>
-      <c r="C13224" s="32"/>
+      <c r="C13224" s="35"/>
     </row>
     <row r="13225" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13225" s="3">
@@ -61509,10 +61509,10 @@
     </row>
     <row r="13274" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13274" s="17"/>
-      <c r="B13274" s="33" t="s">
+      <c r="B13274" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="C13274" s="34"/>
+      <c r="C13274" s="33"/>
     </row>
     <row r="13275" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13275" s="5" t="s">
@@ -62489,19 +62489,19 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B13462" s="7"/>
-      <c r="C13462" s="32" t="s">
+      <c r="C13462" s="35" t="s">
         <v>583</v>
       </c>
     </row>
     <row r="13463" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13463" s="3"/>
       <c r="B13463" s="7"/>
-      <c r="C13463" s="32"/>
+      <c r="C13463" s="35"/>
     </row>
     <row r="13464" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13464" s="3"/>
       <c r="B13464" s="7"/>
-      <c r="C13464" s="32"/>
+      <c r="C13464" s="35"/>
     </row>
     <row r="13465" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13465" s="3">
@@ -62998,14 +62998,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B13580" s="7"/>
-      <c r="C13580" s="32" t="s">
+      <c r="C13580" s="35" t="s">
         <v>586</v>
       </c>
     </row>
     <row r="13581" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13581" s="3"/>
       <c r="B13581" s="7"/>
-      <c r="C13581" s="32"/>
+      <c r="C13581" s="35"/>
     </row>
     <row r="13582" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13582" s="3">
@@ -63238,7 +63238,7 @@
       <c r="A13644" s="25">
         <v>7.2</v>
       </c>
-      <c r="B13644" s="35" t="s">
+      <c r="B13644" s="34" t="s">
         <v>342</v>
       </c>
       <c r="C13644" s="11" t="s">
@@ -63247,7 +63247,7 @@
     </row>
     <row r="13645" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13645" s="25"/>
-      <c r="B13645" s="35"/>
+      <c r="B13645" s="34"/>
       <c r="C13645" s="11"/>
     </row>
     <row r="13646" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -63559,14 +63559,14 @@
         <v>2.1</v>
       </c>
       <c r="B13692" s="7"/>
-      <c r="C13692" s="32" t="s">
+      <c r="C13692" s="35" t="s">
         <v>589</v>
       </c>
     </row>
     <row r="13693" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13693" s="3"/>
       <c r="B13693" s="7"/>
-      <c r="C13693" s="32"/>
+      <c r="C13693" s="35"/>
     </row>
     <row r="13694" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13694" s="3">
@@ -64203,7 +64203,7 @@
       <c r="A13933" s="25">
         <v>4.2</v>
       </c>
-      <c r="B13933" s="35" t="s">
+      <c r="B13933" s="34" t="s">
         <v>514</v>
       </c>
       <c r="C13933" s="11" t="s">
@@ -64212,7 +64212,7 @@
     </row>
     <row r="13934" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13934" s="25"/>
-      <c r="B13934" s="35"/>
+      <c r="B13934" s="34"/>
       <c r="C13934" s="11"/>
     </row>
     <row r="13935" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -64220,19 +64220,19 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B13935" s="2"/>
-      <c r="C13935" s="32" t="s">
+      <c r="C13935" s="35" t="s">
         <v>583</v>
       </c>
     </row>
     <row r="13936" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13936" s="3"/>
       <c r="B13936" s="2"/>
-      <c r="C13936" s="32"/>
+      <c r="C13936" s="35"/>
     </row>
     <row r="13937" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13937" s="3"/>
       <c r="B13937" s="2"/>
-      <c r="C13937" s="32"/>
+      <c r="C13937" s="35"/>
     </row>
     <row r="13938" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13938" s="3">
@@ -64363,7 +64363,7 @@
       <c r="A13992" s="25">
         <v>4.2</v>
       </c>
-      <c r="B13992" s="35" t="s">
+      <c r="B13992" s="34" t="s">
         <v>514</v>
       </c>
       <c r="C13992" s="11" t="s">
@@ -64372,7 +64372,7 @@
     </row>
     <row r="13993" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13993" s="25"/>
-      <c r="B13993" s="35"/>
+      <c r="B13993" s="34"/>
       <c r="C13993" s="11"/>
     </row>
     <row r="13994" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -64632,10 +64632,10 @@
     </row>
     <row r="14041" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14041" s="17"/>
-      <c r="B14041" s="33" t="s">
+      <c r="B14041" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="C14041" s="34"/>
+      <c r="C14041" s="33"/>
     </row>
     <row r="14042" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14042" s="5" t="s">
@@ -64730,7 +64730,7 @@
       <c r="A14051" s="23">
         <v>4.2</v>
       </c>
-      <c r="B14051" s="35" t="s">
+      <c r="B14051" s="34" t="s">
         <v>514</v>
       </c>
       <c r="C14051" s="11" t="s">
@@ -64739,7 +64739,7 @@
     </row>
     <row r="14052" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14052" s="23"/>
-      <c r="B14052" s="35"/>
+      <c r="B14052" s="34"/>
       <c r="C14052" s="11"/>
     </row>
     <row r="14053" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -64747,14 +64747,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B14053" s="7"/>
-      <c r="C14053" s="32" t="s">
+      <c r="C14053" s="35" t="s">
         <v>586</v>
       </c>
     </row>
     <row r="14054" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14054" s="3"/>
       <c r="B14054" s="7"/>
-      <c r="C14054" s="32"/>
+      <c r="C14054" s="35"/>
     </row>
     <row r="14055" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14055" s="3">
@@ -64776,7 +64776,7 @@
       <c r="A14057" s="23">
         <v>6.2</v>
       </c>
-      <c r="B14057" s="35" t="s">
+      <c r="B14057" s="34" t="s">
         <v>515</v>
       </c>
       <c r="C14057" s="11" t="s">
@@ -64785,7 +64785,7 @@
     </row>
     <row r="14058" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14058" s="23"/>
-      <c r="B14058" s="35"/>
+      <c r="B14058" s="34"/>
       <c r="C14058" s="11"/>
     </row>
     <row r="14059" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -64962,7 +64962,7 @@
       <c r="A14112" s="25">
         <v>5.2</v>
       </c>
-      <c r="B14112" s="35" t="s">
+      <c r="B14112" s="34" t="s">
         <v>343</v>
       </c>
       <c r="C14112" s="11" t="s">
@@ -64971,7 +64971,7 @@
     </row>
     <row r="14113" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14113" s="25"/>
-      <c r="B14113" s="35"/>
+      <c r="B14113" s="34"/>
       <c r="C14113" s="11"/>
     </row>
     <row r="14114" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -65336,10 +65336,10 @@
     </row>
     <row r="14218" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14218" s="17"/>
-      <c r="B14218" s="33" t="s">
+      <c r="B14218" s="32" t="s">
         <v>122</v>
       </c>
-      <c r="C14218" s="34"/>
+      <c r="C14218" s="33"/>
     </row>
     <row r="14219" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14219" s="5" t="s">
@@ -65510,7 +65510,7 @@
       <c r="A14238" s="25">
         <v>7.2</v>
       </c>
-      <c r="B14238" s="35" t="s">
+      <c r="B14238" s="34" t="s">
         <v>342</v>
       </c>
       <c r="C14238" s="11" t="s">
@@ -65519,7 +65519,7 @@
     </row>
     <row r="14239" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14239" s="25"/>
-      <c r="B14239" s="35"/>
+      <c r="B14239" s="34"/>
       <c r="C14239" s="11"/>
     </row>
     <row r="14240" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -66173,10 +66173,10 @@
     </row>
     <row r="14336" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14336" s="17"/>
-      <c r="B14336" s="33" t="s">
+      <c r="B14336" s="32" t="s">
         <v>127</v>
       </c>
-      <c r="C14336" s="34"/>
+      <c r="C14336" s="33"/>
     </row>
     <row r="14337" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14337" s="5" t="s">
@@ -66331,7 +66331,7 @@
       <c r="A14354" s="25">
         <v>7.2</v>
       </c>
-      <c r="B14354" s="35" t="s">
+      <c r="B14354" s="34" t="s">
         <v>342</v>
       </c>
       <c r="C14354" s="11" t="s">
@@ -66340,7 +66340,7 @@
     </row>
     <row r="14355" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14355" s="25"/>
-      <c r="B14355" s="35"/>
+      <c r="B14355" s="34"/>
       <c r="C14355" s="11"/>
     </row>
     <row r="14356" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -67117,10 +67117,10 @@
     </row>
     <row r="14513" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14513" s="17"/>
-      <c r="B14513" s="33" t="s">
+      <c r="B14513" s="32" t="s">
         <v>223</v>
       </c>
-      <c r="C14513" s="34"/>
+      <c r="C14513" s="33"/>
     </row>
     <row r="14514" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14514" s="5" t="s">
@@ -67237,14 +67237,14 @@
         <v>6.1</v>
       </c>
       <c r="B14526" s="7"/>
-      <c r="C14526" s="32" t="s">
+      <c r="C14526" s="35" t="s">
         <v>586</v>
       </c>
     </row>
     <row r="14527" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14527" s="3"/>
       <c r="B14527" s="7"/>
-      <c r="C14527" s="32"/>
+      <c r="C14527" s="35"/>
     </row>
     <row r="14528" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14528" s="3">
@@ -67329,10 +67329,10 @@
     </row>
     <row r="14572" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14572" s="17"/>
-      <c r="B14572" s="33" t="s">
+      <c r="B14572" s="32" t="s">
         <v>139</v>
       </c>
-      <c r="C14572" s="34"/>
+      <c r="C14572" s="33"/>
     </row>
     <row r="14573" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14573" s="5" t="s">
@@ -67984,7 +67984,7 @@
       <c r="A14706" s="23">
         <v>5.2</v>
       </c>
-      <c r="B14706" s="35" t="s">
+      <c r="B14706" s="34" t="s">
         <v>342</v>
       </c>
       <c r="C14706" s="11" t="s">
@@ -67993,7 +67993,7 @@
     </row>
     <row r="14707" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14707" s="23"/>
-      <c r="B14707" s="35"/>
+      <c r="B14707" s="34"/>
       <c r="C14707" s="11"/>
     </row>
     <row r="14708" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -68353,14 +68353,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B14760" s="7"/>
-      <c r="C14760" s="32" t="s">
+      <c r="C14760" s="35" t="s">
         <v>612</v>
       </c>
     </row>
     <row r="14761" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14761" s="3"/>
       <c r="B14761" s="7"/>
-      <c r="C14761" s="32"/>
+      <c r="C14761" s="35"/>
     </row>
     <row r="14762" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14762" s="3">
@@ -68445,14 +68445,14 @@
         <v>2.1</v>
       </c>
       <c r="B14813" s="7"/>
-      <c r="C14813" s="32" t="s">
+      <c r="C14813" s="35" t="s">
         <v>614</v>
       </c>
     </row>
     <row r="14814" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14814" s="3"/>
       <c r="B14814" s="7"/>
-      <c r="C14814" s="32"/>
+      <c r="C14814" s="35"/>
     </row>
     <row r="14815" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14815" s="3">
@@ -68485,10 +68485,10 @@
     </row>
     <row r="14867" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14867" s="17"/>
-      <c r="B14867" s="33" t="s">
+      <c r="B14867" s="32" t="s">
         <v>619</v>
       </c>
-      <c r="C14867" s="34"/>
+      <c r="C14867" s="33"/>
     </row>
     <row r="14868" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14868" s="5" t="s">
@@ -68829,7 +68829,7 @@
       <c r="A14942" s="25">
         <v>5.2</v>
       </c>
-      <c r="B14942" s="35" t="s">
+      <c r="B14942" s="34" t="s">
         <v>342</v>
       </c>
       <c r="C14942" s="11" t="s">
@@ -68838,7 +68838,7 @@
     </row>
     <row r="14943" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14943" s="25"/>
-      <c r="B14943" s="35"/>
+      <c r="B14943" s="34"/>
       <c r="C14943" s="11"/>
     </row>
     <row r="14944" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -69098,10 +69098,10 @@
     </row>
     <row r="14985" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14985" s="17"/>
-      <c r="B14985" s="33" t="s">
+      <c r="B14985" s="32" t="s">
         <v>153</v>
       </c>
-      <c r="C14985" s="34"/>
+      <c r="C14985" s="33"/>
     </row>
     <row r="14986" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14986" s="5" t="s">
@@ -69224,7 +69224,7 @@
       <c r="A14999" s="23">
         <v>5.2</v>
       </c>
-      <c r="B14999" s="35" t="s">
+      <c r="B14999" s="34" t="s">
         <v>342</v>
       </c>
       <c r="C14999" s="11" t="s">
@@ -69233,7 +69233,7 @@
     </row>
     <row r="15000" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15000" s="23"/>
-      <c r="B15000" s="35"/>
+      <c r="B15000" s="34"/>
       <c r="C15000" s="11"/>
     </row>
     <row r="15001" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -69241,14 +69241,14 @@
         <v>6.1</v>
       </c>
       <c r="B15001" s="7"/>
-      <c r="C15001" s="32" t="s">
+      <c r="C15001" s="35" t="s">
         <v>586</v>
       </c>
     </row>
     <row r="15002" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15002" s="3"/>
       <c r="B15002" s="7"/>
-      <c r="C15002" s="32"/>
+      <c r="C15002" s="35"/>
     </row>
     <row r="15003" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15003" s="3">
@@ -69270,7 +69270,7 @@
       <c r="A15005" s="23">
         <v>7.2</v>
       </c>
-      <c r="B15005" s="35" t="s">
+      <c r="B15005" s="34" t="s">
         <v>344</v>
       </c>
       <c r="C15005" s="11" t="s">
@@ -69279,7 +69279,7 @@
     </row>
     <row r="15006" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15006" s="23"/>
-      <c r="B15006" s="35"/>
+      <c r="B15006" s="34"/>
       <c r="C15006" s="11"/>
     </row>
     <row r="15007" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -69470,7 +69470,7 @@
       <c r="A15058" s="25">
         <v>5.2</v>
       </c>
-      <c r="B15058" s="35" t="s">
+      <c r="B15058" s="34" t="s">
         <v>342</v>
       </c>
       <c r="C15058" s="11" t="s">
@@ -69479,7 +69479,7 @@
     </row>
     <row r="15059" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15059" s="25"/>
-      <c r="B15059" s="35"/>
+      <c r="B15059" s="34"/>
       <c r="C15059" s="11"/>
     </row>
     <row r="15060" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -69728,53 +69728,273 @@
     </row>
   </sheetData>
   <mergeCells count="338">
-    <mergeCell ref="B14867:C14867"/>
-    <mergeCell ref="B14942:B14943"/>
-    <mergeCell ref="B14985:C14985"/>
-    <mergeCell ref="C15001:C15002"/>
-    <mergeCell ref="B14999:B15000"/>
-    <mergeCell ref="B15005:B15006"/>
-    <mergeCell ref="B15058:B15059"/>
-    <mergeCell ref="B14513:C14513"/>
-    <mergeCell ref="C14526:C14527"/>
-    <mergeCell ref="B14572:C14572"/>
-    <mergeCell ref="B14706:B14707"/>
-    <mergeCell ref="C14760:C14761"/>
-    <mergeCell ref="C14813:C14814"/>
-    <mergeCell ref="B14112:B14113"/>
-    <mergeCell ref="B14218:C14218"/>
-    <mergeCell ref="B14238:B14239"/>
-    <mergeCell ref="B14354:B14355"/>
-    <mergeCell ref="B14336:C14336"/>
-    <mergeCell ref="C13935:C13937"/>
-    <mergeCell ref="B13933:B13934"/>
-    <mergeCell ref="B13992:B13993"/>
-    <mergeCell ref="B14051:B14052"/>
-    <mergeCell ref="B14057:B14058"/>
-    <mergeCell ref="C14053:C14054"/>
-    <mergeCell ref="B14041:C14041"/>
-    <mergeCell ref="B13274:C13274"/>
-    <mergeCell ref="C13462:C13464"/>
-    <mergeCell ref="C13580:C13581"/>
-    <mergeCell ref="B13644:B13645"/>
-    <mergeCell ref="C13692:C13693"/>
-    <mergeCell ref="B13117:B13118"/>
-    <mergeCell ref="B13170:B13171"/>
-    <mergeCell ref="C13172:C13174"/>
-    <mergeCell ref="C13222:C13224"/>
-    <mergeCell ref="B12991:B12993"/>
-    <mergeCell ref="B13054:B13055"/>
-    <mergeCell ref="C13056:C13058"/>
-    <mergeCell ref="B13097:C13097"/>
-    <mergeCell ref="C13113:C13114"/>
-    <mergeCell ref="B13111:B13112"/>
-    <mergeCell ref="C12820:C12822"/>
-    <mergeCell ref="B12818:B12819"/>
-    <mergeCell ref="C12579:C12581"/>
-    <mergeCell ref="C12638:C12639"/>
-    <mergeCell ref="B12684:C12684"/>
-    <mergeCell ref="B12702:B12703"/>
-    <mergeCell ref="C12704:C12706"/>
+    <mergeCell ref="B7433:C7433"/>
+    <mergeCell ref="C7449:C7451"/>
+    <mergeCell ref="B7447:B7448"/>
+    <mergeCell ref="B7038:B7039"/>
+    <mergeCell ref="C7208:C7209"/>
+    <mergeCell ref="B7154:B7155"/>
+    <mergeCell ref="B5618:B5619"/>
+    <mergeCell ref="B5566:B5567"/>
+    <mergeCell ref="C6501:C6503"/>
+    <mergeCell ref="B6548:C6548"/>
+    <mergeCell ref="C6258:C6260"/>
+    <mergeCell ref="B6371:C6371"/>
+    <mergeCell ref="B6489:C6489"/>
+    <mergeCell ref="C6028:C6030"/>
+    <mergeCell ref="C6146:C6147"/>
+    <mergeCell ref="C4677:C4678"/>
+    <mergeCell ref="B4781:C4781"/>
+    <mergeCell ref="B1846:B1847"/>
+    <mergeCell ref="B3733:B3734"/>
+    <mergeCell ref="C5504:C5505"/>
+    <mergeCell ref="B4663:C4663"/>
+    <mergeCell ref="C4803:C4804"/>
+    <mergeCell ref="C4557:C4558"/>
+    <mergeCell ref="C4616:C4618"/>
+    <mergeCell ref="B4604:C4604"/>
+    <mergeCell ref="B5502:B5503"/>
+    <mergeCell ref="B5722:C5722"/>
+    <mergeCell ref="C5561:C5563"/>
+    <mergeCell ref="B5604:C5604"/>
+    <mergeCell ref="C5620:C5621"/>
+    <mergeCell ref="B5663:C5663"/>
+    <mergeCell ref="B5427:C5427"/>
+    <mergeCell ref="B1794:B1795"/>
+    <mergeCell ref="B1787:B1788"/>
+    <mergeCell ref="B3681:B3682"/>
+    <mergeCell ref="B3674:B3675"/>
+    <mergeCell ref="B5559:B5560"/>
+    <mergeCell ref="B3381:B3382"/>
+    <mergeCell ref="B5266:B5267"/>
+    <mergeCell ref="B5545:C5545"/>
+    <mergeCell ref="C5155:C5156"/>
+    <mergeCell ref="C5268:C5269"/>
+    <mergeCell ref="B5076:C5076"/>
+    <mergeCell ref="C5089:C5091"/>
+    <mergeCell ref="B4958:C4958"/>
+    <mergeCell ref="C4969:C4970"/>
+    <mergeCell ref="C5030:C5031"/>
+    <mergeCell ref="C4855:C4856"/>
+    <mergeCell ref="C4919:C4920"/>
+    <mergeCell ref="B4899:C4899"/>
+    <mergeCell ref="B4801:B4802"/>
+    <mergeCell ref="B1377:B1378"/>
+    <mergeCell ref="B3265:B3266"/>
+    <mergeCell ref="B5153:B5154"/>
+    <mergeCell ref="B899:B900"/>
+    <mergeCell ref="B2787:B2788"/>
+    <mergeCell ref="B4675:B4676"/>
+    <mergeCell ref="B1493:B1494"/>
+    <mergeCell ref="B1142:B1143"/>
+    <mergeCell ref="B3029:B3030"/>
+    <mergeCell ref="B4917:B4918"/>
+    <mergeCell ref="C2196:C2197"/>
+    <mergeCell ref="B2244:C2244"/>
+    <mergeCell ref="B2303:C2303"/>
+    <mergeCell ref="C1966:C1967"/>
+    <mergeCell ref="B2008:C2008"/>
+    <mergeCell ref="C2078:C2079"/>
+    <mergeCell ref="C4316:C4317"/>
+    <mergeCell ref="C4373:C4374"/>
+    <mergeCell ref="B4191:C4191"/>
+    <mergeCell ref="C4209:C4210"/>
+    <mergeCell ref="C4084:C4085"/>
+    <mergeCell ref="B4073:C4073"/>
+    <mergeCell ref="B4132:C4132"/>
+    <mergeCell ref="C4143:C4145"/>
+    <mergeCell ref="B4014:C4014"/>
+    <mergeCell ref="C4025:C4026"/>
+    <mergeCell ref="B2319:B2320"/>
+    <mergeCell ref="B4207:B4208"/>
+    <mergeCell ref="B2913:B2914"/>
+    <mergeCell ref="B3011:C3011"/>
+    <mergeCell ref="C3031:C3032"/>
+    <mergeCell ref="C3083:C3085"/>
+    <mergeCell ref="B2893:C2893"/>
+    <mergeCell ref="C1848:C1849"/>
+    <mergeCell ref="B1949:C1949"/>
+    <mergeCell ref="C1731:C1732"/>
+    <mergeCell ref="C1789:C1791"/>
+    <mergeCell ref="B1772:C1772"/>
+    <mergeCell ref="C2915:C2916"/>
+    <mergeCell ref="B2952:C2952"/>
+    <mergeCell ref="C2967:C2968"/>
+    <mergeCell ref="C2428:C2429"/>
+    <mergeCell ref="C2485:C2487"/>
+    <mergeCell ref="B2716:C2716"/>
+    <mergeCell ref="C2728:C2730"/>
+    <mergeCell ref="B2775:C2775"/>
+    <mergeCell ref="C2789:C2790"/>
+    <mergeCell ref="B2539:C2539"/>
+    <mergeCell ref="C2610:C2612"/>
+    <mergeCell ref="C2669:C2670"/>
+    <mergeCell ref="C2321:C2322"/>
+    <mergeCell ref="C2255:C2257"/>
+    <mergeCell ref="C2137:C2139"/>
+    <mergeCell ref="C1541:C1542"/>
+    <mergeCell ref="B1654:C1654"/>
+    <mergeCell ref="C1666:C1667"/>
+    <mergeCell ref="C840:C842"/>
+    <mergeCell ref="C901:C902"/>
+    <mergeCell ref="C1193:C1194"/>
+    <mergeCell ref="B1182:C1182"/>
+    <mergeCell ref="C1027:C1028"/>
+    <mergeCell ref="B1005:C1005"/>
+    <mergeCell ref="C1079:C1080"/>
+    <mergeCell ref="B1123:C1123"/>
+    <mergeCell ref="B1025:B1026"/>
+    <mergeCell ref="C781:C782"/>
+    <mergeCell ref="B1477:C1477"/>
+    <mergeCell ref="C1495:C1496"/>
+    <mergeCell ref="C1313:C1315"/>
+    <mergeCell ref="B1359:C1359"/>
+    <mergeCell ref="C1379:C1380"/>
+    <mergeCell ref="A27:C30"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="C249:C250"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="A141:C146"/>
+    <mergeCell ref="A147:C147"/>
+    <mergeCell ref="C190:C191"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="C597:C598"/>
+    <mergeCell ref="C308:C309"/>
+    <mergeCell ref="C367:C369"/>
+    <mergeCell ref="C433:C434"/>
+    <mergeCell ref="C540:C541"/>
+    <mergeCell ref="B1300:C1300"/>
+    <mergeCell ref="C1254:C1255"/>
+    <mergeCell ref="C1144:C1145"/>
+    <mergeCell ref="B431:B432"/>
+    <mergeCell ref="B3247:C3247"/>
+    <mergeCell ref="C3267:C3268"/>
+    <mergeCell ref="C3142:C3143"/>
+    <mergeCell ref="B3188:C3188"/>
+    <mergeCell ref="C3201:C3203"/>
+    <mergeCell ref="C3560:C3562"/>
+    <mergeCell ref="B3558:B3559"/>
+    <mergeCell ref="C3618:C3619"/>
+    <mergeCell ref="B3660:C3660"/>
+    <mergeCell ref="C3676:C3678"/>
+    <mergeCell ref="B3365:C3365"/>
+    <mergeCell ref="C3383:C3384"/>
+    <mergeCell ref="C3429:C3430"/>
+    <mergeCell ref="B3955:C3955"/>
+    <mergeCell ref="C3966:C3967"/>
+    <mergeCell ref="C3854:C3855"/>
+    <mergeCell ref="B3837:C3837"/>
+    <mergeCell ref="B3719:C3719"/>
+    <mergeCell ref="C3735:C3736"/>
+    <mergeCell ref="B3616:B3617"/>
+    <mergeCell ref="C8146:C8147"/>
+    <mergeCell ref="B8572:B8573"/>
+    <mergeCell ref="B8554:C8554"/>
+    <mergeCell ref="B8690:B8691"/>
+    <mergeCell ref="B8672:C8672"/>
+    <mergeCell ref="B5781:C5781"/>
+    <mergeCell ref="B7610:C7610"/>
+    <mergeCell ref="B7669:C7669"/>
+    <mergeCell ref="B7980:B7981"/>
+    <mergeCell ref="C8028:C8029"/>
+    <mergeCell ref="B6961:C6961"/>
+    <mergeCell ref="C6974:C6976"/>
+    <mergeCell ref="B7020:C7020"/>
+    <mergeCell ref="B6784:C6784"/>
+    <mergeCell ref="B6802:B6803"/>
+    <mergeCell ref="B6666:C6666"/>
+    <mergeCell ref="B6686:B6687"/>
+    <mergeCell ref="B6560:B6561"/>
+    <mergeCell ref="B6092:B6093"/>
+    <mergeCell ref="B6076:C6076"/>
+    <mergeCell ref="B7454:B7455"/>
+    <mergeCell ref="B7506:B7507"/>
+    <mergeCell ref="B7315:C7315"/>
+    <mergeCell ref="B7390:B7391"/>
+    <mergeCell ref="C9149:C9150"/>
+    <mergeCell ref="B9276:B9277"/>
+    <mergeCell ref="B9335:B9336"/>
+    <mergeCell ref="B9394:B9395"/>
+    <mergeCell ref="C9446:C9447"/>
+    <mergeCell ref="B9498:C9498"/>
+    <mergeCell ref="C9516:C9517"/>
+    <mergeCell ref="B8926:B8927"/>
+    <mergeCell ref="B8908:C8908"/>
+    <mergeCell ref="C8972:C8973"/>
+    <mergeCell ref="B9040:B9041"/>
+    <mergeCell ref="C9870:C9871"/>
+    <mergeCell ref="B9868:B9869"/>
+    <mergeCell ref="C9977:C9978"/>
+    <mergeCell ref="C10034:C10035"/>
+    <mergeCell ref="C9564:C9565"/>
+    <mergeCell ref="C9627:C9628"/>
+    <mergeCell ref="C9686:C9687"/>
+    <mergeCell ref="C9745:C9746"/>
+    <mergeCell ref="C9804:C9805"/>
+    <mergeCell ref="B10442:C10442"/>
+    <mergeCell ref="C10516:C10517"/>
+    <mergeCell ref="B10560:C10560"/>
+    <mergeCell ref="C10159:C10160"/>
+    <mergeCell ref="C10218:C10219"/>
+    <mergeCell ref="B10336:B10337"/>
+    <mergeCell ref="C10338:C10339"/>
+    <mergeCell ref="C9916:C9917"/>
+    <mergeCell ref="C10277:C10278"/>
+    <mergeCell ref="C10816:C10817"/>
+    <mergeCell ref="B10814:B10815"/>
+    <mergeCell ref="B10796:C10796"/>
+    <mergeCell ref="B10578:B10579"/>
+    <mergeCell ref="C10580:C10581"/>
+    <mergeCell ref="C10632:C10633"/>
+    <mergeCell ref="C10691:C10692"/>
+    <mergeCell ref="C10750:C10751"/>
+    <mergeCell ref="B10462:B10463"/>
+    <mergeCell ref="C10464:C10465"/>
+    <mergeCell ref="B11225:B11226"/>
+    <mergeCell ref="C11227:C11228"/>
+    <mergeCell ref="B11282:B11283"/>
+    <mergeCell ref="C11284:C11285"/>
+    <mergeCell ref="B10930:B10931"/>
+    <mergeCell ref="C10932:C10933"/>
+    <mergeCell ref="C10978:C10979"/>
+    <mergeCell ref="C11037:C11038"/>
+    <mergeCell ref="B11107:B11108"/>
+    <mergeCell ref="C11109:C11110"/>
+    <mergeCell ref="C12165:C12166"/>
+    <mergeCell ref="B12224:B12225"/>
+    <mergeCell ref="C12226:C12228"/>
+    <mergeCell ref="B779:B780"/>
+    <mergeCell ref="B12045:B12046"/>
+    <mergeCell ref="B12104:B12105"/>
+    <mergeCell ref="B12169:B12170"/>
+    <mergeCell ref="B12163:B12164"/>
+    <mergeCell ref="C11804:C11805"/>
+    <mergeCell ref="C11865:C11867"/>
+    <mergeCell ref="C11922:C11923"/>
+    <mergeCell ref="C12047:C12049"/>
+    <mergeCell ref="C11633:C11635"/>
+    <mergeCell ref="C11692:C11693"/>
+    <mergeCell ref="B11681:C11681"/>
+    <mergeCell ref="C11758:C11760"/>
+    <mergeCell ref="B11756:B11757"/>
+    <mergeCell ref="C11334:C11336"/>
+    <mergeCell ref="B11386:C11386"/>
+    <mergeCell ref="C11404:C11406"/>
+    <mergeCell ref="C11515:C11517"/>
+    <mergeCell ref="C11574:C11576"/>
+    <mergeCell ref="B11166:B11167"/>
+    <mergeCell ref="C11168:C11169"/>
+    <mergeCell ref="B720:B721"/>
+    <mergeCell ref="B838:B839"/>
+    <mergeCell ref="B845:B846"/>
+    <mergeCell ref="B1664:B1665"/>
+    <mergeCell ref="B1670:B1671"/>
+    <mergeCell ref="B2726:B2727"/>
+    <mergeCell ref="B2733:B2734"/>
+    <mergeCell ref="B2608:B2609"/>
+    <mergeCell ref="B2667:B2668"/>
+    <mergeCell ref="B1729:B1730"/>
     <mergeCell ref="B12448:C12448"/>
     <mergeCell ref="B12466:B12467"/>
     <mergeCell ref="C12468:C12470"/>
@@ -69799,273 +70019,53 @@
     <mergeCell ref="B9213:B9214"/>
     <mergeCell ref="C12106:C12108"/>
     <mergeCell ref="B12153:C12153"/>
-    <mergeCell ref="B720:B721"/>
-    <mergeCell ref="B838:B839"/>
-    <mergeCell ref="B845:B846"/>
-    <mergeCell ref="B1664:B1665"/>
-    <mergeCell ref="B1670:B1671"/>
-    <mergeCell ref="B2726:B2727"/>
-    <mergeCell ref="B2733:B2734"/>
-    <mergeCell ref="B2608:B2609"/>
-    <mergeCell ref="B2667:B2668"/>
-    <mergeCell ref="C12165:C12166"/>
-    <mergeCell ref="B12224:B12225"/>
-    <mergeCell ref="C12226:C12228"/>
-    <mergeCell ref="B779:B780"/>
-    <mergeCell ref="B12045:B12046"/>
-    <mergeCell ref="B12104:B12105"/>
-    <mergeCell ref="B12169:B12170"/>
-    <mergeCell ref="B12163:B12164"/>
-    <mergeCell ref="C11804:C11805"/>
-    <mergeCell ref="C11865:C11867"/>
-    <mergeCell ref="C11922:C11923"/>
-    <mergeCell ref="C12047:C12049"/>
-    <mergeCell ref="C11633:C11635"/>
-    <mergeCell ref="C11692:C11693"/>
-    <mergeCell ref="B11681:C11681"/>
-    <mergeCell ref="C11758:C11760"/>
-    <mergeCell ref="B11756:B11757"/>
-    <mergeCell ref="C11334:C11336"/>
-    <mergeCell ref="B11386:C11386"/>
-    <mergeCell ref="C11404:C11406"/>
-    <mergeCell ref="C11515:C11517"/>
-    <mergeCell ref="C11574:C11576"/>
-    <mergeCell ref="B11166:B11167"/>
-    <mergeCell ref="C11168:C11169"/>
-    <mergeCell ref="B11225:B11226"/>
-    <mergeCell ref="C11227:C11228"/>
-    <mergeCell ref="B11282:B11283"/>
-    <mergeCell ref="C11284:C11285"/>
-    <mergeCell ref="B10930:B10931"/>
-    <mergeCell ref="C10932:C10933"/>
-    <mergeCell ref="C10978:C10979"/>
-    <mergeCell ref="C11037:C11038"/>
-    <mergeCell ref="B11107:B11108"/>
-    <mergeCell ref="C11109:C11110"/>
-    <mergeCell ref="C10816:C10817"/>
-    <mergeCell ref="B10814:B10815"/>
-    <mergeCell ref="B10796:C10796"/>
-    <mergeCell ref="B10578:B10579"/>
-    <mergeCell ref="C10580:C10581"/>
-    <mergeCell ref="C10632:C10633"/>
-    <mergeCell ref="C10691:C10692"/>
-    <mergeCell ref="C10750:C10751"/>
-    <mergeCell ref="B10462:B10463"/>
-    <mergeCell ref="C10464:C10465"/>
-    <mergeCell ref="B10442:C10442"/>
-    <mergeCell ref="C10516:C10517"/>
-    <mergeCell ref="B10560:C10560"/>
-    <mergeCell ref="C10159:C10160"/>
-    <mergeCell ref="C10218:C10219"/>
-    <mergeCell ref="B10336:B10337"/>
-    <mergeCell ref="C10338:C10339"/>
-    <mergeCell ref="C9916:C9917"/>
-    <mergeCell ref="C10277:C10278"/>
-    <mergeCell ref="C9870:C9871"/>
-    <mergeCell ref="B9868:B9869"/>
-    <mergeCell ref="C9977:C9978"/>
-    <mergeCell ref="C10034:C10035"/>
-    <mergeCell ref="C9564:C9565"/>
-    <mergeCell ref="C9627:C9628"/>
-    <mergeCell ref="C9686:C9687"/>
-    <mergeCell ref="C9745:C9746"/>
-    <mergeCell ref="C9804:C9805"/>
-    <mergeCell ref="C9149:C9150"/>
-    <mergeCell ref="B9276:B9277"/>
-    <mergeCell ref="B9335:B9336"/>
-    <mergeCell ref="B9394:B9395"/>
-    <mergeCell ref="C9446:C9447"/>
-    <mergeCell ref="B9498:C9498"/>
-    <mergeCell ref="C9516:C9517"/>
-    <mergeCell ref="B8926:B8927"/>
-    <mergeCell ref="B8908:C8908"/>
-    <mergeCell ref="C8972:C8973"/>
-    <mergeCell ref="B9040:B9041"/>
-    <mergeCell ref="C8146:C8147"/>
-    <mergeCell ref="B8572:B8573"/>
-    <mergeCell ref="B8554:C8554"/>
-    <mergeCell ref="B8690:B8691"/>
-    <mergeCell ref="B8672:C8672"/>
-    <mergeCell ref="B5781:C5781"/>
-    <mergeCell ref="B7610:C7610"/>
-    <mergeCell ref="B7669:C7669"/>
-    <mergeCell ref="B7980:B7981"/>
-    <mergeCell ref="C8028:C8029"/>
-    <mergeCell ref="B6961:C6961"/>
-    <mergeCell ref="C6974:C6976"/>
-    <mergeCell ref="B7020:C7020"/>
-    <mergeCell ref="B6784:C6784"/>
-    <mergeCell ref="B6802:B6803"/>
-    <mergeCell ref="B6666:C6666"/>
-    <mergeCell ref="B6686:B6687"/>
-    <mergeCell ref="B6560:B6561"/>
-    <mergeCell ref="C3676:C3678"/>
-    <mergeCell ref="B3365:C3365"/>
-    <mergeCell ref="C3383:C3384"/>
-    <mergeCell ref="C3429:C3430"/>
-    <mergeCell ref="B3955:C3955"/>
-    <mergeCell ref="C3966:C3967"/>
-    <mergeCell ref="C3854:C3855"/>
-    <mergeCell ref="B3837:C3837"/>
-    <mergeCell ref="B3719:C3719"/>
-    <mergeCell ref="C3735:C3736"/>
-    <mergeCell ref="B3616:B3617"/>
-    <mergeCell ref="B3247:C3247"/>
-    <mergeCell ref="C3267:C3268"/>
-    <mergeCell ref="C3142:C3143"/>
-    <mergeCell ref="B3188:C3188"/>
-    <mergeCell ref="C3201:C3203"/>
-    <mergeCell ref="C3560:C3562"/>
-    <mergeCell ref="B3558:B3559"/>
-    <mergeCell ref="C3618:C3619"/>
-    <mergeCell ref="B3660:C3660"/>
-    <mergeCell ref="B1729:B1730"/>
-    <mergeCell ref="C781:C782"/>
-    <mergeCell ref="B1477:C1477"/>
-    <mergeCell ref="C1495:C1496"/>
-    <mergeCell ref="C1313:C1315"/>
-    <mergeCell ref="B1359:C1359"/>
-    <mergeCell ref="C1379:C1380"/>
-    <mergeCell ref="A27:C30"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="C249:C250"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="A141:C146"/>
-    <mergeCell ref="A147:C147"/>
-    <mergeCell ref="C190:C191"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="C597:C598"/>
-    <mergeCell ref="C308:C309"/>
-    <mergeCell ref="C367:C369"/>
-    <mergeCell ref="C433:C434"/>
-    <mergeCell ref="C540:C541"/>
-    <mergeCell ref="B1300:C1300"/>
-    <mergeCell ref="C1254:C1255"/>
-    <mergeCell ref="C1144:C1145"/>
-    <mergeCell ref="C1541:C1542"/>
-    <mergeCell ref="B1654:C1654"/>
-    <mergeCell ref="C1666:C1667"/>
-    <mergeCell ref="C840:C842"/>
-    <mergeCell ref="C901:C902"/>
-    <mergeCell ref="C1193:C1194"/>
-    <mergeCell ref="B1182:C1182"/>
-    <mergeCell ref="C1027:C1028"/>
-    <mergeCell ref="B1005:C1005"/>
-    <mergeCell ref="C1079:C1080"/>
-    <mergeCell ref="B1123:C1123"/>
-    <mergeCell ref="B3011:C3011"/>
-    <mergeCell ref="C3031:C3032"/>
-    <mergeCell ref="C3083:C3085"/>
-    <mergeCell ref="B2893:C2893"/>
-    <mergeCell ref="C1848:C1849"/>
-    <mergeCell ref="B1949:C1949"/>
-    <mergeCell ref="C1731:C1732"/>
-    <mergeCell ref="C1789:C1791"/>
-    <mergeCell ref="B1772:C1772"/>
-    <mergeCell ref="C2915:C2916"/>
-    <mergeCell ref="B2952:C2952"/>
-    <mergeCell ref="C2967:C2968"/>
-    <mergeCell ref="C2428:C2429"/>
-    <mergeCell ref="C2485:C2487"/>
-    <mergeCell ref="B2716:C2716"/>
-    <mergeCell ref="C2728:C2730"/>
-    <mergeCell ref="B2775:C2775"/>
-    <mergeCell ref="C2789:C2790"/>
-    <mergeCell ref="B2539:C2539"/>
-    <mergeCell ref="C2610:C2612"/>
-    <mergeCell ref="C2669:C2670"/>
-    <mergeCell ref="C2321:C2322"/>
-    <mergeCell ref="C2255:C2257"/>
-    <mergeCell ref="C2137:C2139"/>
-    <mergeCell ref="C2196:C2197"/>
-    <mergeCell ref="B2244:C2244"/>
-    <mergeCell ref="B2303:C2303"/>
-    <mergeCell ref="C1966:C1967"/>
-    <mergeCell ref="B2008:C2008"/>
-    <mergeCell ref="C2078:C2079"/>
-    <mergeCell ref="C4316:C4317"/>
-    <mergeCell ref="C4373:C4374"/>
-    <mergeCell ref="B4191:C4191"/>
-    <mergeCell ref="C4209:C4210"/>
-    <mergeCell ref="C4084:C4085"/>
-    <mergeCell ref="B4073:C4073"/>
-    <mergeCell ref="B4132:C4132"/>
-    <mergeCell ref="C4143:C4145"/>
-    <mergeCell ref="B4014:C4014"/>
-    <mergeCell ref="C4025:C4026"/>
-    <mergeCell ref="B431:B432"/>
-    <mergeCell ref="B2319:B2320"/>
-    <mergeCell ref="B4207:B4208"/>
-    <mergeCell ref="B6092:B6093"/>
-    <mergeCell ref="B1025:B1026"/>
-    <mergeCell ref="B2913:B2914"/>
-    <mergeCell ref="B4801:B4802"/>
-    <mergeCell ref="B1377:B1378"/>
-    <mergeCell ref="B3265:B3266"/>
-    <mergeCell ref="B5153:B5154"/>
-    <mergeCell ref="B899:B900"/>
-    <mergeCell ref="B2787:B2788"/>
-    <mergeCell ref="B4675:B4676"/>
-    <mergeCell ref="B1493:B1494"/>
-    <mergeCell ref="B1142:B1143"/>
-    <mergeCell ref="B3029:B3030"/>
-    <mergeCell ref="B4917:B4918"/>
-    <mergeCell ref="B6076:C6076"/>
-    <mergeCell ref="B5722:C5722"/>
-    <mergeCell ref="C5561:C5563"/>
-    <mergeCell ref="B5604:C5604"/>
-    <mergeCell ref="C5620:C5621"/>
-    <mergeCell ref="B5663:C5663"/>
-    <mergeCell ref="B5427:C5427"/>
-    <mergeCell ref="B1794:B1795"/>
-    <mergeCell ref="B1787:B1788"/>
-    <mergeCell ref="B3681:B3682"/>
-    <mergeCell ref="B3674:B3675"/>
-    <mergeCell ref="B5559:B5560"/>
-    <mergeCell ref="B3381:B3382"/>
-    <mergeCell ref="B5266:B5267"/>
-    <mergeCell ref="B5545:C5545"/>
-    <mergeCell ref="C5155:C5156"/>
-    <mergeCell ref="C5268:C5269"/>
-    <mergeCell ref="B5076:C5076"/>
-    <mergeCell ref="C5089:C5091"/>
-    <mergeCell ref="B4958:C4958"/>
-    <mergeCell ref="C4969:C4970"/>
-    <mergeCell ref="C5030:C5031"/>
-    <mergeCell ref="C4855:C4856"/>
-    <mergeCell ref="C4919:C4920"/>
-    <mergeCell ref="B4899:C4899"/>
-    <mergeCell ref="C4677:C4678"/>
-    <mergeCell ref="B4781:C4781"/>
-    <mergeCell ref="B1846:B1847"/>
-    <mergeCell ref="B3733:B3734"/>
-    <mergeCell ref="C5504:C5505"/>
-    <mergeCell ref="B4663:C4663"/>
-    <mergeCell ref="C4803:C4804"/>
-    <mergeCell ref="C4557:C4558"/>
-    <mergeCell ref="C4616:C4618"/>
-    <mergeCell ref="B4604:C4604"/>
-    <mergeCell ref="B7454:B7455"/>
-    <mergeCell ref="B7506:B7507"/>
-    <mergeCell ref="B7315:C7315"/>
-    <mergeCell ref="B7390:B7391"/>
-    <mergeCell ref="B7433:C7433"/>
-    <mergeCell ref="C7449:C7451"/>
-    <mergeCell ref="B7447:B7448"/>
-    <mergeCell ref="B7038:B7039"/>
-    <mergeCell ref="C7208:C7209"/>
-    <mergeCell ref="B7154:B7155"/>
-    <mergeCell ref="B5618:B5619"/>
-    <mergeCell ref="B5566:B5567"/>
-    <mergeCell ref="C6501:C6503"/>
-    <mergeCell ref="B6548:C6548"/>
-    <mergeCell ref="C6258:C6260"/>
-    <mergeCell ref="B6371:C6371"/>
-    <mergeCell ref="B6489:C6489"/>
-    <mergeCell ref="C6028:C6030"/>
-    <mergeCell ref="C6146:C6147"/>
-    <mergeCell ref="B5502:B5503"/>
+    <mergeCell ref="B12991:B12993"/>
+    <mergeCell ref="B13054:B13055"/>
+    <mergeCell ref="C13056:C13058"/>
+    <mergeCell ref="B13097:C13097"/>
+    <mergeCell ref="C13113:C13114"/>
+    <mergeCell ref="B13111:B13112"/>
+    <mergeCell ref="C12820:C12822"/>
+    <mergeCell ref="B12818:B12819"/>
+    <mergeCell ref="C12579:C12581"/>
+    <mergeCell ref="C12638:C12639"/>
+    <mergeCell ref="B12684:C12684"/>
+    <mergeCell ref="B12702:B12703"/>
+    <mergeCell ref="C12704:C12706"/>
+    <mergeCell ref="B13274:C13274"/>
+    <mergeCell ref="C13462:C13464"/>
+    <mergeCell ref="C13580:C13581"/>
+    <mergeCell ref="B13644:B13645"/>
+    <mergeCell ref="C13692:C13693"/>
+    <mergeCell ref="B13117:B13118"/>
+    <mergeCell ref="B13170:B13171"/>
+    <mergeCell ref="C13172:C13174"/>
+    <mergeCell ref="C13222:C13224"/>
+    <mergeCell ref="B14112:B14113"/>
+    <mergeCell ref="B14218:C14218"/>
+    <mergeCell ref="B14238:B14239"/>
+    <mergeCell ref="B14354:B14355"/>
+    <mergeCell ref="B14336:C14336"/>
+    <mergeCell ref="C13935:C13937"/>
+    <mergeCell ref="B13933:B13934"/>
+    <mergeCell ref="B13992:B13993"/>
+    <mergeCell ref="B14051:B14052"/>
+    <mergeCell ref="B14057:B14058"/>
+    <mergeCell ref="C14053:C14054"/>
+    <mergeCell ref="B14041:C14041"/>
+    <mergeCell ref="B14867:C14867"/>
+    <mergeCell ref="B14942:B14943"/>
+    <mergeCell ref="B14985:C14985"/>
+    <mergeCell ref="C15001:C15002"/>
+    <mergeCell ref="B14999:B15000"/>
+    <mergeCell ref="B15005:B15006"/>
+    <mergeCell ref="B15058:B15059"/>
+    <mergeCell ref="B14513:C14513"/>
+    <mergeCell ref="C14526:C14527"/>
+    <mergeCell ref="B14572:C14572"/>
+    <mergeCell ref="B14706:B14707"/>
+    <mergeCell ref="C14760:C14761"/>
+    <mergeCell ref="C14813:C14814"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup scale="79" orientation="portrait" r:id="rId1"/>
